--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4830" uniqueCount="1477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4845" uniqueCount="1482">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4216 +207,4231 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-09-08</t>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
   </si>
   <si>
     <t>1529751.922313</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
     <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8048,7 +8063,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E754"/>
+  <dimension ref="A1:E757"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -20863,10 +20878,61 @@
         <v>521</v>
       </c>
       <c r="D754" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E754" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="s">
+        <v>145</v>
+      </c>
+      <c r="B755" t="s">
+        <v>435</v>
+      </c>
+      <c r="C755" t="s">
+        <v>521</v>
+      </c>
+      <c r="D755" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E755" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="s">
+        <v>145</v>
+      </c>
+      <c r="B756" t="s">
+        <v>435</v>
+      </c>
+      <c r="C756" t="s">
+        <v>521</v>
+      </c>
+      <c r="D756" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E756" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="s">
+        <v>145</v>
+      </c>
+      <c r="B757" t="s">
+        <v>435</v>
+      </c>
+      <c r="C757" t="s">
+        <v>521</v>
+      </c>
+      <c r="D757" t="s">
         <v>61</v>
       </c>
-      <c r="E754" t="s">
-        <v>1463</v>
+      <c r="E757" t="s">
+        <v>1468</v>
       </c>
     </row>
   </sheetData>
@@ -20881,13 +20947,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -20895,13 +20961,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -20909,13 +20975,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -20923,13 +20989,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -20937,13 +21003,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -20951,13 +21017,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -20965,13 +21031,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -20979,13 +21045,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -20993,13 +21059,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1467</v>
+        <v>1472</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21017,13 +21083,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21034,13 +21100,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1469</v>
+        <v>1474</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21051,13 +21117,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1470</v>
+        <v>1475</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21068,13 +21134,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21085,13 +21151,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21102,13 +21168,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1473</v>
+        <v>1478</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21119,13 +21185,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1474</v>
+        <v>1479</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21136,13 +21202,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21153,13 +21219,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1466</v>
+        <v>1471</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4845" uniqueCount="1482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4850" uniqueCount="1484">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4231 +207,4237 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
     <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8063,7 +8069,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E757"/>
+  <dimension ref="A1:E758"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -20929,10 +20935,27 @@
         <v>521</v>
       </c>
       <c r="D757" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E757" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="s">
+        <v>145</v>
+      </c>
+      <c r="B758" t="s">
+        <v>435</v>
+      </c>
+      <c r="C758" t="s">
+        <v>521</v>
+      </c>
+      <c r="D758" t="s">
         <v>61</v>
       </c>
-      <c r="E757" t="s">
-        <v>1468</v>
+      <c r="E758" t="s">
+        <v>1470</v>
       </c>
     </row>
   </sheetData>
@@ -20947,13 +20970,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -20961,13 +20984,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -20975,13 +20998,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -20989,13 +21012,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21003,13 +21026,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21017,13 +21040,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21031,13 +21054,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21045,13 +21068,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21059,13 +21082,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21083,13 +21106,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21100,13 +21123,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21117,13 +21140,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21134,13 +21157,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21151,13 +21174,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21168,13 +21191,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21185,13 +21208,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21202,13 +21225,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21219,13 +21242,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4850" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4905" uniqueCount="1500">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4237 +207,4285 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-09-15</t>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>1571716.898813</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>1551896.922313</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
     <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8069,7 +8117,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E758"/>
+  <dimension ref="A1:E769"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -20952,10 +21000,197 @@
         <v>521</v>
       </c>
       <c r="D758" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E758" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="s">
+        <v>145</v>
+      </c>
+      <c r="B759" t="s">
+        <v>435</v>
+      </c>
+      <c r="C759" t="s">
+        <v>521</v>
+      </c>
+      <c r="D759" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E759" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="s">
+        <v>145</v>
+      </c>
+      <c r="B760" t="s">
+        <v>435</v>
+      </c>
+      <c r="C760" t="s">
+        <v>521</v>
+      </c>
+      <c r="D760" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E760" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="s">
+        <v>145</v>
+      </c>
+      <c r="B761" t="s">
+        <v>435</v>
+      </c>
+      <c r="C761" t="s">
+        <v>521</v>
+      </c>
+      <c r="D761" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E761" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="s">
+        <v>145</v>
+      </c>
+      <c r="B762" t="s">
+        <v>435</v>
+      </c>
+      <c r="C762" t="s">
+        <v>521</v>
+      </c>
+      <c r="D762" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E762" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="s">
+        <v>145</v>
+      </c>
+      <c r="B763" t="s">
+        <v>435</v>
+      </c>
+      <c r="C763" t="s">
+        <v>521</v>
+      </c>
+      <c r="D763" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E763" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="s">
+        <v>145</v>
+      </c>
+      <c r="B764" t="s">
+        <v>435</v>
+      </c>
+      <c r="C764" t="s">
+        <v>521</v>
+      </c>
+      <c r="D764" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E764" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="s">
+        <v>630</v>
+      </c>
+      <c r="B765" t="s">
+        <v>522</v>
+      </c>
+      <c r="C765" t="s">
+        <v>521</v>
+      </c>
+      <c r="D765" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E765" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="s">
+        <v>630</v>
+      </c>
+      <c r="B766" t="s">
+        <v>522</v>
+      </c>
+      <c r="C766" t="s">
+        <v>521</v>
+      </c>
+      <c r="D766" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E766" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="s">
+        <v>630</v>
+      </c>
+      <c r="B767" t="s">
+        <v>522</v>
+      </c>
+      <c r="C767" t="s">
+        <v>521</v>
+      </c>
+      <c r="D767" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E767" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="s">
+        <v>630</v>
+      </c>
+      <c r="B768" t="s">
+        <v>522</v>
+      </c>
+      <c r="C768" t="s">
+        <v>521</v>
+      </c>
+      <c r="D768" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E768" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="s">
+        <v>145</v>
+      </c>
+      <c r="B769" t="s">
+        <v>435</v>
+      </c>
+      <c r="C769" t="s">
+        <v>521</v>
+      </c>
+      <c r="D769" t="s">
         <v>61</v>
       </c>
-      <c r="E758" t="s">
-        <v>1470</v>
+      <c r="E769" t="s">
+        <v>1486</v>
       </c>
     </row>
   </sheetData>
@@ -20970,13 +21205,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -20984,13 +21219,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -20998,13 +21233,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21012,13 +21247,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21026,13 +21261,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21040,13 +21275,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21054,13 +21289,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21068,13 +21303,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21082,13 +21317,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1474</v>
+        <v>1490</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21106,13 +21341,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1475</v>
+        <v>1491</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21123,13 +21358,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1476</v>
+        <v>1492</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21140,13 +21375,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1477</v>
+        <v>1493</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21157,13 +21392,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1478</v>
+        <v>1494</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21174,13 +21409,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21191,13 +21426,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1480</v>
+        <v>1496</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21208,13 +21443,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1481</v>
+        <v>1497</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21225,13 +21460,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1482</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21242,13 +21477,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1473</v>
+        <v>1489</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1483</v>
+        <v>1499</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4905" uniqueCount="1500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="1510">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4285 +207,4315 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>1589310.369038</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
   </si>
   <si>
     <t>1571716.898813</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1551896.922313</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1555196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>1557596.922313</t>
-  </si>
-  <si>
-    <t>1563196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>1569596.922313</t>
-  </si>
-  <si>
-    <t>1573596.922313</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>1577196.922313</t>
-  </si>
-  <si>
-    <t>1571716.922313</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>1571386.928313</t>
-  </si>
-  <si>
-    <t>1571056.934313</t>
-  </si>
-  <si>
-    <t>1570726.908813</t>
-  </si>
-  <si>
     <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>1570256.894813</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>1568855.294963</t>
+  </si>
+  <si>
+    <t>1568788.084988</t>
+  </si>
+  <si>
+    <t>1568720.875013</t>
+  </si>
+  <si>
+    <t>1568653.665038</t>
+  </si>
+  <si>
+    <t>1581510.369038</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8117,7 +8147,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E769"/>
+  <dimension ref="A1:E777"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21187,10 +21217,146 @@
         <v>521</v>
       </c>
       <c r="D769" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E769" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="s">
+        <v>690</v>
+      </c>
+      <c r="B770" t="s">
+        <v>522</v>
+      </c>
+      <c r="C770" t="s">
+        <v>521</v>
+      </c>
+      <c r="D770" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E770" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="s">
+        <v>690</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C771" t="s">
+        <v>521</v>
+      </c>
+      <c r="D771" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E771" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="s">
+        <v>690</v>
+      </c>
+      <c r="B772" t="s">
+        <v>522</v>
+      </c>
+      <c r="C772" t="s">
+        <v>521</v>
+      </c>
+      <c r="D772" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E772" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="s">
+        <v>690</v>
+      </c>
+      <c r="B773" t="s">
+        <v>522</v>
+      </c>
+      <c r="C773" t="s">
+        <v>521</v>
+      </c>
+      <c r="D773" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E773" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="s">
+        <v>690</v>
+      </c>
+      <c r="B774" t="s">
+        <v>522</v>
+      </c>
+      <c r="C774" t="s">
+        <v>521</v>
+      </c>
+      <c r="D774" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E774" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="s">
+        <v>690</v>
+      </c>
+      <c r="B775" t="s">
+        <v>522</v>
+      </c>
+      <c r="C775" t="s">
+        <v>521</v>
+      </c>
+      <c r="D775" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E775" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="s">
+        <v>145</v>
+      </c>
+      <c r="B776" t="s">
+        <v>435</v>
+      </c>
+      <c r="C776" t="s">
+        <v>521</v>
+      </c>
+      <c r="D776" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E776" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="s">
+        <v>145</v>
+      </c>
+      <c r="B777" t="s">
+        <v>435</v>
+      </c>
+      <c r="C777" t="s">
+        <v>521</v>
+      </c>
+      <c r="D777" t="s">
         <v>61</v>
       </c>
-      <c r="E769" t="s">
-        <v>1486</v>
+      <c r="E777" t="s">
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -21205,13 +21371,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -21219,13 +21385,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -21233,13 +21399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21247,13 +21413,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21261,13 +21427,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21275,13 +21441,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21289,13 +21455,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21303,13 +21469,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21317,13 +21483,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21341,13 +21507,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21358,13 +21524,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21375,13 +21541,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21392,13 +21558,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21409,13 +21575,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21426,13 +21592,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21443,13 +21609,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21460,13 +21626,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21477,13 +21643,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4945" uniqueCount="1510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4955" uniqueCount="1513">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4315 +207,4324 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-09-26</t>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>1594610.369038</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
+  </si>
+  <si>
+    <t>1571716.898813</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>1570256.894813</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>1568855.294963</t>
+  </si>
+  <si>
+    <t>1568788.084988</t>
+  </si>
+  <si>
+    <t>1568720.875013</t>
+  </si>
+  <si>
+    <t>1568653.665038</t>
+  </si>
+  <si>
+    <t>1581510.369038</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
   <si>
     <t>1589310.369038</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1551896.922313</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1555196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>1557596.922313</t>
-  </si>
-  <si>
-    <t>1563196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>1569596.922313</t>
-  </si>
-  <si>
-    <t>1573596.922313</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>1577196.922313</t>
-  </si>
-  <si>
-    <t>1571716.922313</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>1571386.928313</t>
-  </si>
-  <si>
-    <t>1571056.934313</t>
-  </si>
-  <si>
-    <t>1570726.908813</t>
-  </si>
-  <si>
-    <t>1571716.898813</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>1570256.894813</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>1568855.294963</t>
-  </si>
-  <si>
-    <t>1568788.084988</t>
-  </si>
-  <si>
-    <t>1568720.875013</t>
-  </si>
-  <si>
-    <t>1568653.665038</t>
-  </si>
-  <si>
-    <t>1581510.369038</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
     <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>1592610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8147,7 +8156,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E777"/>
+  <dimension ref="A1:E779"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21353,10 +21362,44 @@
         <v>521</v>
       </c>
       <c r="D777" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E777" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="s">
+        <v>145</v>
+      </c>
+      <c r="B778" t="s">
+        <v>435</v>
+      </c>
+      <c r="C778" t="s">
+        <v>521</v>
+      </c>
+      <c r="D778" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E778" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="s">
+        <v>145</v>
+      </c>
+      <c r="B779" t="s">
+        <v>435</v>
+      </c>
+      <c r="C779" t="s">
+        <v>521</v>
+      </c>
+      <c r="D779" t="s">
         <v>61</v>
       </c>
-      <c r="E777" t="s">
-        <v>1496</v>
+      <c r="E779" t="s">
+        <v>1499</v>
       </c>
     </row>
   </sheetData>
@@ -21371,13 +21414,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -21385,13 +21428,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -21399,13 +21442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21413,13 +21456,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21427,13 +21470,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21441,13 +21484,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21455,13 +21498,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21469,13 +21512,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21483,13 +21526,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21507,13 +21550,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21524,13 +21567,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21541,13 +21584,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21558,13 +21601,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21575,13 +21618,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21592,13 +21635,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21609,13 +21652,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21626,13 +21669,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21643,13 +21686,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4955" uniqueCount="1513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5020" uniqueCount="1530">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4324 +207,4375 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-09-29</t>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>1629343.553538</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
+  </si>
+  <si>
+    <t>1571716.898813</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>1570256.894813</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>1568855.294963</t>
+  </si>
+  <si>
+    <t>1568788.084988</t>
+  </si>
+  <si>
+    <t>1568720.875013</t>
+  </si>
+  <si>
+    <t>1568653.665038</t>
+  </si>
+  <si>
+    <t>1581510.369038</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>1589310.369038</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>1592610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
   </si>
   <si>
     <t>1594610.369038</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1551896.922313</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1555196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>1557596.922313</t>
-  </si>
-  <si>
-    <t>1563196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>1569596.922313</t>
-  </si>
-  <si>
-    <t>1573596.922313</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>1577196.922313</t>
-  </si>
-  <si>
-    <t>1571716.922313</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>1571386.928313</t>
-  </si>
-  <si>
-    <t>1571056.934313</t>
-  </si>
-  <si>
-    <t>1570726.908813</t>
-  </si>
-  <si>
-    <t>1571716.898813</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>1570256.894813</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>1568855.294963</t>
-  </si>
-  <si>
-    <t>1568788.084988</t>
-  </si>
-  <si>
-    <t>1568720.875013</t>
-  </si>
-  <si>
-    <t>1568653.665038</t>
-  </si>
-  <si>
-    <t>1581510.369038</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>1589310.369038</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>1592610.369038</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
+    <t>1595610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>1593458.369038</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>1593247.949038</t>
+  </si>
+  <si>
+    <t>1592917.955038</t>
+  </si>
+  <si>
+    <t>1591897.953538</t>
+  </si>
+  <si>
+    <t>1597977.953538</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>1603227.953538</t>
+  </si>
+  <si>
+    <t>1609227.953538</t>
+  </si>
+  <si>
+    <t>1612827.953538</t>
+  </si>
+  <si>
+    <t>1616427.953538</t>
+  </si>
+  <si>
+    <t>1620027.953538</t>
+  </si>
+  <si>
+    <t>1620552.953538</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8156,7 +8207,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E779"/>
+  <dimension ref="A1:E792"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21396,10 +21447,231 @@
         <v>521</v>
       </c>
       <c r="D779" t="s">
-        <v>61</v>
+        <v>1500</v>
       </c>
       <c r="E779" t="s">
         <v>1499</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="s">
+        <v>145</v>
+      </c>
+      <c r="B780" t="s">
+        <v>435</v>
+      </c>
+      <c r="C780" t="s">
+        <v>521</v>
+      </c>
+      <c r="D780" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E780" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="s">
+        <v>630</v>
+      </c>
+      <c r="B781" t="s">
+        <v>522</v>
+      </c>
+      <c r="C781" t="s">
+        <v>521</v>
+      </c>
+      <c r="D781" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E781" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="s">
+        <v>630</v>
+      </c>
+      <c r="B782" t="s">
+        <v>522</v>
+      </c>
+      <c r="C782" t="s">
+        <v>521</v>
+      </c>
+      <c r="D782" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E782" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="s">
+        <v>630</v>
+      </c>
+      <c r="B783" t="s">
+        <v>522</v>
+      </c>
+      <c r="C783" t="s">
+        <v>521</v>
+      </c>
+      <c r="D783" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E783" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="s">
+        <v>630</v>
+      </c>
+      <c r="B784" t="s">
+        <v>522</v>
+      </c>
+      <c r="C784" t="s">
+        <v>521</v>
+      </c>
+      <c r="D784" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E784" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="s">
+        <v>145</v>
+      </c>
+      <c r="B785" t="s">
+        <v>435</v>
+      </c>
+      <c r="C785" t="s">
+        <v>521</v>
+      </c>
+      <c r="D785" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E785" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="s">
+        <v>104</v>
+      </c>
+      <c r="B786" t="s">
+        <v>435</v>
+      </c>
+      <c r="C786" t="s">
+        <v>521</v>
+      </c>
+      <c r="D786" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E786" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="s">
+        <v>104</v>
+      </c>
+      <c r="B787" t="s">
+        <v>435</v>
+      </c>
+      <c r="C787" t="s">
+        <v>521</v>
+      </c>
+      <c r="D787" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E787" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="s">
+        <v>104</v>
+      </c>
+      <c r="B788" t="s">
+        <v>435</v>
+      </c>
+      <c r="C788" t="s">
+        <v>521</v>
+      </c>
+      <c r="D788" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E788" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="s">
+        <v>104</v>
+      </c>
+      <c r="B789" t="s">
+        <v>435</v>
+      </c>
+      <c r="C789" t="s">
+        <v>521</v>
+      </c>
+      <c r="D789" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E789" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="s">
+        <v>104</v>
+      </c>
+      <c r="B790" t="s">
+        <v>435</v>
+      </c>
+      <c r="C790" t="s">
+        <v>521</v>
+      </c>
+      <c r="D790" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E790" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="s">
+        <v>104</v>
+      </c>
+      <c r="B791" t="s">
+        <v>435</v>
+      </c>
+      <c r="C791" t="s">
+        <v>521</v>
+      </c>
+      <c r="D791" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E791" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="s">
+        <v>145</v>
+      </c>
+      <c r="B792" t="s">
+        <v>435</v>
+      </c>
+      <c r="C792" t="s">
+        <v>521</v>
+      </c>
+      <c r="D792" t="s">
+        <v>61</v>
+      </c>
+      <c r="E792" t="s">
+        <v>1516</v>
       </c>
     </row>
   </sheetData>
@@ -21414,13 +21686,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -21428,13 +21700,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -21442,13 +21714,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21456,13 +21728,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21470,13 +21742,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21484,13 +21756,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21498,13 +21770,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21512,13 +21784,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21526,13 +21798,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1502</v>
+        <v>1519</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1503</v>
+        <v>1520</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21550,13 +21822,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1504</v>
+        <v>1521</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21567,13 +21839,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1505</v>
+        <v>1522</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21584,13 +21856,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1506</v>
+        <v>1523</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21601,13 +21873,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1507</v>
+        <v>1524</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21618,13 +21890,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1508</v>
+        <v>1525</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21635,13 +21907,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1509</v>
+        <v>1526</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21652,13 +21924,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1510</v>
+        <v>1527</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21669,13 +21941,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1511</v>
+        <v>1528</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21686,13 +21958,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1502</v>
+        <v>1519</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1512</v>
+        <v>1529</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5020" uniqueCount="1530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5045" uniqueCount="1539">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4375 +207,4402 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-10-06</t>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>1647649.808038</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
+  </si>
+  <si>
+    <t>1571716.898813</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>1570256.894813</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>1568855.294963</t>
+  </si>
+  <si>
+    <t>1568788.084988</t>
+  </si>
+  <si>
+    <t>1568720.875013</t>
+  </si>
+  <si>
+    <t>1568653.665038</t>
+  </si>
+  <si>
+    <t>1581510.369038</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>1589310.369038</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>1592610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>1594610.369038</t>
+  </si>
+  <si>
+    <t>1595610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>1593458.369038</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>1593247.949038</t>
+  </si>
+  <si>
+    <t>1592917.955038</t>
+  </si>
+  <si>
+    <t>1591897.953538</t>
+  </si>
+  <si>
+    <t>1597977.953538</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>1603227.953538</t>
+  </si>
+  <si>
+    <t>1609227.953538</t>
+  </si>
+  <si>
+    <t>1612827.953538</t>
+  </si>
+  <si>
+    <t>1616427.953538</t>
+  </si>
+  <si>
+    <t>1620027.953538</t>
+  </si>
+  <si>
+    <t>1620552.953538</t>
   </si>
   <si>
     <t>1629343.553538</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1551896.922313</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1555196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>1557596.922313</t>
-  </si>
-  <si>
-    <t>1563196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>1569596.922313</t>
-  </si>
-  <si>
-    <t>1573596.922313</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>1577196.922313</t>
-  </si>
-  <si>
-    <t>1571716.922313</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>1571386.928313</t>
-  </si>
-  <si>
-    <t>1571056.934313</t>
-  </si>
-  <si>
-    <t>1570726.908813</t>
-  </si>
-  <si>
-    <t>1571716.898813</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>1570256.894813</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>1568855.294963</t>
-  </si>
-  <si>
-    <t>1568788.084988</t>
-  </si>
-  <si>
-    <t>1568720.875013</t>
-  </si>
-  <si>
-    <t>1568653.665038</t>
-  </si>
-  <si>
-    <t>1581510.369038</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>1589310.369038</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>1592610.369038</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
-  </si>
-  <si>
-    <t>1594610.369038</t>
-  </si>
-  <si>
-    <t>1595610.369038</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>1593458.369038</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
-  </si>
-  <si>
-    <t>1593247.949038</t>
-  </si>
-  <si>
-    <t>1592917.955038</t>
-  </si>
-  <si>
-    <t>1591897.953538</t>
-  </si>
-  <si>
-    <t>1597977.953538</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>1603227.953538</t>
-  </si>
-  <si>
-    <t>1609227.953538</t>
-  </si>
-  <si>
-    <t>1612827.953538</t>
-  </si>
-  <si>
-    <t>1616427.953538</t>
-  </si>
-  <si>
-    <t>1620027.953538</t>
-  </si>
-  <si>
-    <t>1620552.953538</t>
-  </si>
-  <si>
     <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>1629013.559538</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>1628413.558038</t>
+  </si>
+  <si>
+    <t>1630539.808038</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>1637574.808038</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8207,7 +8234,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E792"/>
+  <dimension ref="A1:E797"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21668,10 +21695,95 @@
         <v>521</v>
       </c>
       <c r="D792" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E792" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="s">
+        <v>630</v>
+      </c>
+      <c r="B793" t="s">
+        <v>522</v>
+      </c>
+      <c r="C793" t="s">
+        <v>521</v>
+      </c>
+      <c r="D793" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E793" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="s">
+        <v>630</v>
+      </c>
+      <c r="B794" t="s">
+        <v>522</v>
+      </c>
+      <c r="C794" t="s">
+        <v>521</v>
+      </c>
+      <c r="D794" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E794" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="s">
+        <v>145</v>
+      </c>
+      <c r="B795" t="s">
+        <v>435</v>
+      </c>
+      <c r="C795" t="s">
+        <v>521</v>
+      </c>
+      <c r="D795" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E795" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="s">
+        <v>145</v>
+      </c>
+      <c r="B796" t="s">
+        <v>435</v>
+      </c>
+      <c r="C796" t="s">
+        <v>521</v>
+      </c>
+      <c r="D796" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E796" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="s">
+        <v>145</v>
+      </c>
+      <c r="B797" t="s">
+        <v>435</v>
+      </c>
+      <c r="C797" t="s">
+        <v>521</v>
+      </c>
+      <c r="D797" t="s">
         <v>61</v>
       </c>
-      <c r="E792" t="s">
-        <v>1516</v>
+      <c r="E797" t="s">
+        <v>1525</v>
       </c>
     </row>
   </sheetData>
@@ -21686,13 +21798,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -21700,13 +21812,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -21714,13 +21826,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21728,13 +21840,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21742,13 +21854,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21756,13 +21868,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21770,13 +21882,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21784,13 +21896,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21798,13 +21910,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21822,13 +21934,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21839,13 +21951,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21856,13 +21968,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1523</v>
+        <v>1532</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21873,13 +21985,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -21890,13 +22002,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1525</v>
+        <v>1534</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -21907,13 +22019,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1526</v>
+        <v>1535</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -21924,13 +22036,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -21941,13 +22053,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -21958,13 +22070,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>

--- a/Acc.xlsx
+++ b/Acc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5045" uniqueCount="1539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5085" uniqueCount="1554">
   <si>
     <t>car_insurance</t>
   </si>
@@ -207,4402 +207,4447 @@
     <t>SHIVAM PROVISION STORE</t>
   </si>
   <si>
-    <t>2026-10-13</t>
+    <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>1666275.530538</t>
+  </si>
+  <si>
+    <t>utkarsh</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>pick_n_pay_store</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>46068</t>
+  </si>
+  <si>
+    <t>2020-04-19</t>
+  </si>
+  <si>
+    <t>55635</t>
+  </si>
+  <si>
+    <t>2020-05-03</t>
+  </si>
+  <si>
+    <t>42309</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>deena_nath_and_sons</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>2020-04-20</t>
+  </si>
+  <si>
+    <t>29250</t>
+  </si>
+  <si>
+    <t>2020-05-02</t>
+  </si>
+  <si>
+    <t>gupta_dal_mills</t>
+  </si>
+  <si>
+    <t>42900</t>
+  </si>
+  <si>
+    <t>2020-05-23</t>
+  </si>
+  <si>
+    <t>21630</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>n_b_traders</t>
+  </si>
+  <si>
+    <t>10550</t>
+  </si>
+  <si>
+    <t>2020-05-09</t>
+  </si>
+  <si>
+    <t>naman_enterprises</t>
+  </si>
+  <si>
+    <t>15330</t>
+  </si>
+  <si>
+    <t>raj_shree_distributors</t>
+  </si>
+  <si>
+    <t>4118</t>
+  </si>
+  <si>
+    <t>ram_niwas_sarveshwar_kumar</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>29646</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>24232</t>
+  </si>
+  <si>
+    <t>2020-05-30</t>
+  </si>
+  <si>
+    <t>21575</t>
+  </si>
+  <si>
+    <t>2020-06-06</t>
+  </si>
+  <si>
+    <t>parul_traders</t>
+  </si>
+  <si>
+    <t>18821</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>palm_tree_hotel_and_restaurent</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>43652</t>
+  </si>
+  <si>
+    <t>65785</t>
+  </si>
+  <si>
+    <t>2020-06-20</t>
+  </si>
+  <si>
+    <t>55984</t>
+  </si>
+  <si>
+    <t>21739</t>
+  </si>
+  <si>
+    <t>17620</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>ganga_traders</t>
+  </si>
+  <si>
+    <t>28917</t>
+  </si>
+  <si>
+    <t>2020-07-08</t>
+  </si>
+  <si>
+    <t>6420</t>
+  </si>
+  <si>
+    <t>40875</t>
+  </si>
+  <si>
+    <t>2020-07-06</t>
+  </si>
+  <si>
+    <t>56311</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>25880</t>
+  </si>
+  <si>
+    <t>17750</t>
+  </si>
+  <si>
+    <t>42278</t>
+  </si>
+  <si>
+    <t>2020-07-10</t>
+  </si>
+  <si>
+    <t>sohan_lal_shri_kishan_das</t>
+  </si>
+  <si>
+    <t>22450</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>52465</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>krishna_enterprises</t>
+  </si>
+  <si>
+    <t>742</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>33390</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>34780</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>sagar_and_co</t>
+  </si>
+  <si>
+    <t>8664</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>vinod_kumar_pramod_kumar</t>
+  </si>
+  <si>
+    <t>19373</t>
+  </si>
+  <si>
+    <t>2020-08-11</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>2020-07-09</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>33768</t>
+  </si>
+  <si>
+    <t>2020-09-20</t>
+  </si>
+  <si>
+    <t>48634</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>78960</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>66511</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>82598</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>29474</t>
+  </si>
+  <si>
+    <t>2020-08-08</t>
+  </si>
+  <si>
+    <t>43498</t>
+  </si>
+  <si>
+    <t>39550</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>26333</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>amar_distributors</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>26460</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>21945</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>10811</t>
+  </si>
+  <si>
+    <t>2020-10-15</t>
+  </si>
+  <si>
+    <t>22260</t>
+  </si>
+  <si>
+    <t>2020-10-17</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>2020-10-26</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>9548</t>
+  </si>
+  <si>
+    <t>2020-10-07</t>
+  </si>
+  <si>
+    <t>5414</t>
+  </si>
+  <si>
+    <t>85205</t>
+  </si>
+  <si>
+    <t>22948</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>125752</t>
+  </si>
+  <si>
+    <t>105819</t>
+  </si>
+  <si>
+    <t>2020-11-08</t>
+  </si>
+  <si>
+    <t>28618</t>
+  </si>
+  <si>
+    <t>107210</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>24600</t>
+  </si>
+  <si>
+    <t>royal_marketing_group</t>
+  </si>
+  <si>
+    <t>25700</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>2020-12-05</t>
+  </si>
+  <si>
+    <t>26360</t>
+  </si>
+  <si>
+    <t>2020-12-07</t>
+  </si>
+  <si>
+    <t>242194</t>
+  </si>
+  <si>
+    <t>64450</t>
+  </si>
+  <si>
+    <t>46525</t>
+  </si>
+  <si>
+    <t>2020-12-06</t>
+  </si>
+  <si>
+    <t>46704</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>48657</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>26200</t>
+  </si>
+  <si>
+    <t>2020-12-27</t>
+  </si>
+  <si>
+    <t>34860</t>
+  </si>
+  <si>
+    <t>32810</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
+  </si>
+  <si>
+    <t>6254</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>162431</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>250974</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>16533</t>
+  </si>
+  <si>
+    <t>2020-12-20</t>
+  </si>
+  <si>
+    <t>15771</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>radhey_dipartmental</t>
+  </si>
+  <si>
+    <t>15955</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>2021-01-20</t>
+  </si>
+  <si>
+    <t>43550</t>
+  </si>
+  <si>
+    <t>maa_ganga_enterprises</t>
+  </si>
+  <si>
+    <t>26136</t>
+  </si>
+  <si>
+    <t>58500</t>
+  </si>
+  <si>
+    <t>64880</t>
+  </si>
+  <si>
+    <t>28560</t>
+  </si>
+  <si>
+    <t>49800</t>
+  </si>
+  <si>
+    <t>2021-03-22</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>2021-03-20</t>
+  </si>
+  <si>
+    <t>31215</t>
+  </si>
+  <si>
+    <t>194205</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>56050</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>202607</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>110752</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>148920</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>31122</t>
+  </si>
+  <si>
+    <t>2021-03-24</t>
+  </si>
+  <si>
+    <t>33750</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>27600</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>102710</t>
+  </si>
+  <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>80350</t>
+  </si>
+  <si>
+    <t>2021-03-21</t>
+  </si>
+  <si>
+    <t>47250</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>10500</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>44083.39</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>43250</t>
+  </si>
+  <si>
+    <t>34020</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>46050</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>30150</t>
+  </si>
+  <si>
+    <t>2021-03-31</t>
+  </si>
+  <si>
+    <t>26880</t>
+  </si>
+  <si>
+    <t>2021-04-07</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>27201</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>2021-04-28</t>
+  </si>
+  <si>
+    <t>36536</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>28201</t>
+  </si>
+  <si>
+    <t>77606</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>23880</t>
+  </si>
+  <si>
+    <t>10030</t>
+  </si>
+  <si>
+    <t>5434</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>1400</t>
+  </si>
+  <si>
+    <t>2021-01-03</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>124571</t>
+  </si>
+  <si>
+    <t>2021-03-25</t>
+  </si>
+  <si>
+    <t>51474</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>26246</t>
+  </si>
+  <si>
+    <t>35767</t>
+  </si>
+  <si>
+    <t>17714</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>35266</t>
+  </si>
+  <si>
+    <t>39178</t>
+  </si>
+  <si>
+    <t>25316</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>8987</t>
+  </si>
+  <si>
+    <t>21147</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>2021-05-11</t>
+  </si>
+  <si>
+    <t>59970</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>54990</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>860</t>
+  </si>
+  <si>
+    <t>47870</t>
+  </si>
+  <si>
+    <t>5670</t>
+  </si>
+  <si>
+    <t>15335</t>
+  </si>
+  <si>
+    <t>91440</t>
+  </si>
+  <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
+    <t>17430</t>
+  </si>
+  <si>
+    <t>royal_marketing_company</t>
+  </si>
+  <si>
+    <t>35040</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>41300</t>
+  </si>
+  <si>
+    <t>2021-10-13</t>
+  </si>
+  <si>
+    <t>29510</t>
+  </si>
+  <si>
+    <t>2021-06-14</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>2021-07-02</t>
+  </si>
+  <si>
+    <t>24350</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>3430</t>
+  </si>
+  <si>
+    <t>39740</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-17</t>
+  </si>
+  <si>
+    <t>38310</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>25200</t>
+  </si>
+  <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>2021-08-21</t>
+  </si>
+  <si>
+    <t>34200</t>
+  </si>
+  <si>
+    <t>33600</t>
+  </si>
+  <si>
+    <t>31200</t>
+  </si>
+  <si>
+    <t>34240</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>9264</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>32700</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>54540</t>
+  </si>
+  <si>
+    <t>41060</t>
+  </si>
+  <si>
+    <t>49156</t>
+  </si>
+  <si>
+    <t>48114</t>
+  </si>
+  <si>
+    <t>2021-09-21</t>
+  </si>
+  <si>
+    <t>chanchal_trading_company</t>
+  </si>
+  <si>
+    <t>18250</t>
+  </si>
+  <si>
+    <t>2021-08-08</t>
+  </si>
+  <si>
+    <t>97950</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>118530</t>
+  </si>
+  <si>
+    <t>9200</t>
+  </si>
+  <si>
+    <t>2021-06-19</t>
+  </si>
+  <si>
+    <t>74076</t>
+  </si>
+  <si>
+    <t>2021-05-29</t>
+  </si>
+  <si>
+    <t>33364</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>87172</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>40982</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>20905</t>
+  </si>
+  <si>
+    <t>121062</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>178358</t>
+  </si>
+  <si>
+    <t>117540</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>158935</t>
+  </si>
+  <si>
+    <t>96721</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>22244</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>25401</t>
+  </si>
+  <si>
+    <t>19234</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>24311</t>
+  </si>
+  <si>
+    <t>26391</t>
+  </si>
+  <si>
+    <t>15155</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>23339</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>16045</t>
+  </si>
+  <si>
+    <t>2021-05-22</t>
+  </si>
+  <si>
+    <t>20762</t>
+  </si>
+  <si>
+    <t>5692</t>
+  </si>
+  <si>
+    <t>9280</t>
+  </si>
+  <si>
+    <t>2021-06-29</t>
+  </si>
+  <si>
+    <t>11999</t>
+  </si>
+  <si>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>8320</t>
+  </si>
+  <si>
+    <t>2021-07-17</t>
+  </si>
+  <si>
+    <t>10370</t>
+  </si>
+  <si>
+    <t>31531</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>13039</t>
+  </si>
+  <si>
+    <t>13717</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>14203</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>9894</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>2021-10-24</t>
+  </si>
+  <si>
+    <t>-79649</t>
+  </si>
+  <si>
+    <t>167596.95</t>
+  </si>
+  <si>
+    <t>-97079</t>
+  </si>
+  <si>
+    <t>sale</t>
+  </si>
+  <si>
+    <t>168576.95</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>169566.95</t>
+  </si>
+  <si>
+    <t>170526.95</t>
+  </si>
+  <si>
+    <t>172046.95</t>
+  </si>
+  <si>
+    <t>2021-08-14</t>
+  </si>
+  <si>
+    <t>174796.95</t>
+  </si>
+  <si>
+    <t>175046.95</t>
+  </si>
+  <si>
+    <t>177170.95</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
+  </si>
+  <si>
+    <t>-132119</t>
+  </si>
+  <si>
+    <t>-173419</t>
+  </si>
+  <si>
+    <t>-202929</t>
+  </si>
+  <si>
+    <t>-216929</t>
+  </si>
+  <si>
+    <t>-241279</t>
+  </si>
+  <si>
+    <t>-244709</t>
+  </si>
+  <si>
+    <t>-284449</t>
+  </si>
+  <si>
+    <t>-344449</t>
+  </si>
+  <si>
+    <t>-382759</t>
+  </si>
+  <si>
+    <t>-407959</t>
+  </si>
+  <si>
+    <t>-441959</t>
+  </si>
+  <si>
+    <t>-476159</t>
+  </si>
+  <si>
+    <t>-509759</t>
+  </si>
+  <si>
+    <t>-540959</t>
+  </si>
+  <si>
+    <t>-564959</t>
+  </si>
+  <si>
+    <t>-599199</t>
+  </si>
+  <si>
+    <t>167906.95</t>
+  </si>
+  <si>
+    <t>135206.95</t>
+  </si>
+  <si>
+    <t>-631749</t>
+  </si>
+  <si>
+    <t>-686289</t>
+  </si>
+  <si>
+    <t>-727349</t>
+  </si>
+  <si>
+    <t>-776505</t>
+  </si>
+  <si>
+    <t>-824619</t>
+  </si>
+  <si>
+    <t>116956.95</t>
+  </si>
+  <si>
+    <t>36956.95</t>
+  </si>
+  <si>
+    <t>-922569</t>
+  </si>
+  <si>
+    <t>-982569</t>
+  </si>
+  <si>
+    <t>-1034569</t>
+  </si>
+  <si>
+    <t>-1153099</t>
+  </si>
+  <si>
+    <t>-1143899</t>
+  </si>
+  <si>
+    <t>-1069823</t>
+  </si>
+  <si>
+    <t>-1036459</t>
+  </si>
+  <si>
+    <t>-949287</t>
+  </si>
+  <si>
+    <t>-908305</t>
+  </si>
+  <si>
+    <t>-808305</t>
+  </si>
+  <si>
+    <t>-787400</t>
+  </si>
+  <si>
+    <t>-666338</t>
+  </si>
+  <si>
+    <t>-487980</t>
+  </si>
+  <si>
+    <t>-370440</t>
+  </si>
+  <si>
+    <t>-211505</t>
+  </si>
+  <si>
+    <t>-114784</t>
+  </si>
+  <si>
+    <t>-92540</t>
+  </si>
+  <si>
+    <t>-67139</t>
+  </si>
+  <si>
+    <t>-47905</t>
+  </si>
+  <si>
+    <t>-23594</t>
+  </si>
+  <si>
+    <t>2797</t>
+  </si>
+  <si>
+    <t>17952</t>
+  </si>
+  <si>
+    <t>41291</t>
+  </si>
+  <si>
+    <t>71791</t>
+  </si>
+  <si>
+    <t>87836</t>
+  </si>
+  <si>
+    <t>108598</t>
+  </si>
+  <si>
+    <t>114290</t>
+  </si>
+  <si>
+    <t>123570</t>
+  </si>
+  <si>
+    <t>135569</t>
+  </si>
+  <si>
+    <t>139234</t>
+  </si>
+  <si>
+    <t>147554</t>
+  </si>
+  <si>
+    <t>157924</t>
+  </si>
+  <si>
+    <t>189455</t>
+  </si>
+  <si>
+    <t>196430</t>
+  </si>
+  <si>
+    <t>209469</t>
+  </si>
+  <si>
+    <t>223186</t>
+  </si>
+  <si>
+    <t>237389</t>
+  </si>
+  <si>
+    <t>247283</t>
+  </si>
+  <si>
+    <t>expns</t>
+  </si>
+  <si>
+    <t>246080</t>
+  </si>
+  <si>
+    <t>36956.96</t>
+  </si>
+  <si>
+    <t>238942</t>
+  </si>
+  <si>
+    <t>218942</t>
+  </si>
+  <si>
+    <t>218895</t>
+  </si>
+  <si>
+    <t>195775</t>
+  </si>
+  <si>
+    <t>176775</t>
+  </si>
+  <si>
+    <t>126775</t>
+  </si>
+  <si>
+    <t>125775</t>
+  </si>
+  <si>
+    <t>105775</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>72275</t>
+  </si>
+  <si>
+    <t>pur</t>
+  </si>
+  <si>
+    <t>32231.96</t>
+  </si>
+  <si>
+    <t>2022-05-29</t>
+  </si>
+  <si>
+    <t>27931.96</t>
+  </si>
+  <si>
+    <t>28281.96</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>28951.96</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>30351.96</t>
+  </si>
+  <si>
+    <t>31791.96</t>
+  </si>
+  <si>
+    <t>33791.96</t>
+  </si>
+  <si>
+    <t>35991.96</t>
+  </si>
+  <si>
+    <t>38241.96</t>
+  </si>
+  <si>
+    <t>40481.96</t>
+  </si>
+  <si>
+    <t>44681.96</t>
+  </si>
+  <si>
+    <t>46571.96</t>
+  </si>
+  <si>
+    <t>2023-05-11</t>
+  </si>
+  <si>
+    <t>48524.96</t>
+  </si>
+  <si>
+    <t>49847.96</t>
+  </si>
+  <si>
+    <t>51149.96</t>
+  </si>
+  <si>
+    <t>52150.72</t>
+  </si>
+  <si>
+    <t>56000.72</t>
+  </si>
+  <si>
+    <t>2023-12-09</t>
+  </si>
+  <si>
+    <t>61209.72</t>
+  </si>
+  <si>
+    <t>65292.12</t>
+  </si>
+  <si>
+    <t>2024-01-14</t>
+  </si>
+  <si>
+    <t>70692.12</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>72342.12</t>
+  </si>
+  <si>
+    <t>2024-01-18</t>
+  </si>
+  <si>
+    <t>74042.12</t>
+  </si>
+  <si>
+    <t>77042.12</t>
+  </si>
+  <si>
+    <t>78082.12</t>
+  </si>
+  <si>
+    <t>81127.12</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>84172.12</t>
+  </si>
+  <si>
+    <t>87847.12</t>
+  </si>
+  <si>
+    <t>94421.52</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>110421.52</t>
+  </si>
+  <si>
+    <t>2024-03-09</t>
+  </si>
+  <si>
+    <t>112821.52</t>
+  </si>
+  <si>
+    <t>116271.52</t>
+  </si>
+  <si>
+    <t>120171.52</t>
+  </si>
+  <si>
+    <t>132381.52</t>
+  </si>
+  <si>
+    <t>2024-03-12</t>
+  </si>
+  <si>
+    <t>133181.52</t>
+  </si>
+  <si>
+    <t>2024-03-13</t>
+  </si>
+  <si>
+    <t>134481.52</t>
+  </si>
+  <si>
+    <t>135941.52</t>
+  </si>
+  <si>
+    <t>134796.81</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>135479.31</t>
+  </si>
+  <si>
+    <t>2024-05-15</t>
+  </si>
+  <si>
+    <t>136975.56</t>
+  </si>
+  <si>
+    <t>137684.31</t>
+  </si>
+  <si>
+    <t>138524.31</t>
+  </si>
+  <si>
+    <t>2024-05-20</t>
+  </si>
+  <si>
+    <t>139364.31</t>
+  </si>
+  <si>
+    <t>140724.31</t>
+  </si>
+  <si>
+    <t>141974.31</t>
+  </si>
+  <si>
+    <t>2024-05-22</t>
+  </si>
+  <si>
+    <t>144274.31</t>
+  </si>
+  <si>
+    <t>146974.31</t>
+  </si>
+  <si>
+    <t>2024-05-27</t>
+  </si>
+  <si>
+    <t>151354.31</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>151794.31</t>
+  </si>
+  <si>
+    <t>154754.31</t>
+  </si>
+  <si>
+    <t>156194.31</t>
+  </si>
+  <si>
+    <t>166851.81</t>
+  </si>
+  <si>
+    <t>167943.81</t>
+  </si>
+  <si>
+    <t>168321.81</t>
+  </si>
+  <si>
+    <t>169067.31</t>
+  </si>
+  <si>
+    <t>169959.81</t>
+  </si>
+  <si>
+    <t>170406.06</t>
+  </si>
+  <si>
+    <t>171078.06</t>
+  </si>
+  <si>
+    <t>173430.06</t>
+  </si>
+  <si>
+    <t>174585.06</t>
+  </si>
+  <si>
+    <t>177063.06</t>
+  </si>
+  <si>
+    <t>CITY_TRADERS</t>
+  </si>
+  <si>
+    <t>172570.56</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>174010.56</t>
+  </si>
+  <si>
+    <t>2024-07-03</t>
+  </si>
+  <si>
+    <t>175760.56</t>
+  </si>
+  <si>
+    <t>2024-07-12</t>
+  </si>
+  <si>
+    <t>176960.56</t>
+  </si>
+  <si>
+    <t>179260.56</t>
+  </si>
+  <si>
+    <t>182334.97</t>
+  </si>
+  <si>
+    <t>2024-07-01</t>
+  </si>
+  <si>
+    <t>185274.97</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>186975.97</t>
+  </si>
+  <si>
+    <t>189285.97</t>
+  </si>
+  <si>
+    <t>192285.97</t>
+  </si>
+  <si>
+    <t>195435.97</t>
+  </si>
+  <si>
+    <t>205935.97</t>
+  </si>
+  <si>
+    <t>206959.72</t>
+  </si>
+  <si>
+    <t>219349.72</t>
+  </si>
+  <si>
+    <t>221554.72</t>
+  </si>
+  <si>
+    <t>222279.22</t>
+  </si>
+  <si>
+    <t>222725.47</t>
+  </si>
+  <si>
+    <t>223066.72</t>
+  </si>
+  <si>
+    <t>225347.31</t>
+  </si>
+  <si>
+    <t>2024-07-13</t>
+  </si>
+  <si>
+    <t>223847.31</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>city_traders</t>
+  </si>
+  <si>
+    <t>220247.31</t>
+  </si>
+  <si>
+    <t>2024-07-11</t>
+  </si>
+  <si>
+    <t>221545.11</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>224594.31</t>
+  </si>
+  <si>
+    <t>225455.31</t>
+  </si>
+  <si>
+    <t>2024-07-24</t>
+  </si>
+  <si>
+    <t>225896.31</t>
+  </si>
+  <si>
+    <t>226796.31</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>227716.31</t>
+  </si>
+  <si>
+    <t>228966.31</t>
+  </si>
+  <si>
+    <t>2024-07-25</t>
+  </si>
+  <si>
+    <t>229286.31</t>
+  </si>
+  <si>
+    <t>235286.31</t>
+  </si>
+  <si>
+    <t>2024-07-30</t>
+  </si>
+  <si>
+    <t>238286.31</t>
+  </si>
+  <si>
+    <t>244686.31</t>
+  </si>
+  <si>
+    <t>251886.31</t>
+  </si>
+  <si>
+    <t>253136.31</t>
+  </si>
+  <si>
+    <t>257936.31</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>266336.3</t>
+  </si>
+  <si>
+    <t>268436.3</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>268676.3</t>
+  </si>
+  <si>
+    <t>2024-08-16</t>
+  </si>
+  <si>
+    <t>271526.3</t>
+  </si>
+  <si>
+    <t>284231.3</t>
+  </si>
+  <si>
+    <t>289691.3</t>
+  </si>
+  <si>
+    <t>293208.8</t>
+  </si>
+  <si>
+    <t>295098.8</t>
+  </si>
+  <si>
+    <t>296610.8</t>
+  </si>
+  <si>
+    <t>297925.7</t>
+  </si>
+  <si>
+    <t>2024-08-12</t>
+  </si>
+  <si>
+    <t>298597.7</t>
+  </si>
+  <si>
+    <t>2024-08-13</t>
+  </si>
+  <si>
+    <t>297881.66</t>
+  </si>
+  <si>
+    <t>2024-08-10</t>
+  </si>
+  <si>
+    <t>299681.7</t>
+  </si>
+  <si>
+    <t>2024-08-25</t>
+  </si>
+  <si>
+    <t>300681.7</t>
+  </si>
+  <si>
+    <t>2024-09-02</t>
+  </si>
+  <si>
+    <t>303481.7</t>
+  </si>
+  <si>
+    <t>309331.7</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>305731.7</t>
+  </si>
+  <si>
+    <t>2024-09-21</t>
+  </si>
+  <si>
+    <t>298006.72</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>304006.7</t>
+  </si>
+  <si>
+    <t>2024-09-18</t>
+  </si>
+  <si>
+    <t>306506.7</t>
+  </si>
+  <si>
+    <t>307706.7</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>309356.7</t>
+  </si>
+  <si>
+    <t>311996.7</t>
+  </si>
+  <si>
+    <t>313296.7</t>
+  </si>
+  <si>
+    <t>314146.7</t>
+  </si>
+  <si>
+    <t>dev_goldiee_agency</t>
+  </si>
+  <si>
+    <t>312346.66</t>
+  </si>
+  <si>
+    <t>2024-10-08</t>
+  </si>
+  <si>
+    <t>Bhotika_Marketing_Group</t>
+  </si>
+  <si>
+    <t>309597.06</t>
+  </si>
+  <si>
+    <t>2024-10-04</t>
+  </si>
+  <si>
+    <t>311697.06</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>311627.06</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>311557.06</t>
+  </si>
+  <si>
+    <t>311322.06</t>
+  </si>
+  <si>
+    <t>301084.56</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>290269.56</t>
+  </si>
+  <si>
+    <t>275149.56</t>
+  </si>
+  <si>
+    <t>271138.56</t>
+  </si>
+  <si>
+    <t>264334.56</t>
+  </si>
+  <si>
+    <t>264194.56</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>264072.06</t>
+  </si>
+  <si>
+    <t>263837.06</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>263767.06</t>
+  </si>
+  <si>
+    <t>263697.06</t>
+  </si>
+  <si>
+    <t>263627.06</t>
+  </si>
+  <si>
+    <t>263557.06</t>
+  </si>
+  <si>
+    <t>262596.94</t>
+  </si>
+  <si>
+    <t>2024-11-08</t>
+  </si>
+  <si>
+    <t>264496.94</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>265896.94</t>
+  </si>
+  <si>
+    <t>268096.94</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>268346.94</t>
+  </si>
+  <si>
+    <t>271846.94</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>272476.94</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>273106.94</t>
+  </si>
+  <si>
+    <t>273036.94</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>272966.94</t>
+  </si>
+  <si>
+    <t>272721.94</t>
+  </si>
+  <si>
+    <t>272529.94</t>
+  </si>
+  <si>
+    <t>276080.34</t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>277880.34</t>
+  </si>
+  <si>
+    <t>280880.34</t>
+  </si>
+  <si>
+    <t>282130.34</t>
+  </si>
+  <si>
+    <t>289630.34</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>294630.44</t>
+  </si>
+  <si>
+    <t>297780.44</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>301230.44</t>
+  </si>
+  <si>
+    <t>306690.44</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>308065.44</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>309797.94</t>
+  </si>
+  <si>
+    <t>2024-12-29</t>
+  </si>
+  <si>
+    <t>310327.12</t>
+  </si>
+  <si>
+    <t>315932.03</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>321270.03</t>
+  </si>
+  <si>
+    <t>316694.12</t>
+  </si>
+  <si>
+    <t>2025-01-13</t>
+  </si>
+  <si>
+    <t>318458.12</t>
+  </si>
+  <si>
+    <t>321765.62</t>
+  </si>
+  <si>
+    <t>323970.62</t>
+  </si>
+  <si>
+    <t>328370.62</t>
+  </si>
+  <si>
+    <t>2025-01-09</t>
+  </si>
+  <si>
+    <t>330220.62</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>332120.62</t>
+  </si>
+  <si>
+    <t>2025-01-20</t>
+  </si>
+  <si>
+    <t>334020.62</t>
+  </si>
+  <si>
+    <t>336420.62</t>
+  </si>
+  <si>
+    <t>340320.62</t>
+  </si>
+  <si>
+    <t>341520.62</t>
+  </si>
+  <si>
+    <t>343120.62</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>343690.62</t>
+  </si>
+  <si>
+    <t>345040.62</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>351040.62</t>
+  </si>
+  <si>
+    <t>353751.03</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>354647.03</t>
+  </si>
+  <si>
+    <t>361747.03</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>366397.03</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>367279.03</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>368161.03</t>
+  </si>
+  <si>
+    <t>369368.53</t>
+  </si>
+  <si>
+    <t>368927.53</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>369452.53</t>
+  </si>
+  <si>
+    <t>369715.03</t>
+  </si>
+  <si>
+    <t>370114.03</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>370555.03</t>
+  </si>
+  <si>
+    <t>404323.03</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>414223.03</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>409873.03</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>416023.03</t>
+  </si>
+  <si>
+    <t>418523.03</t>
+  </si>
+  <si>
+    <t>2025-02-19</t>
+  </si>
+  <si>
+    <t>419923.03</t>
+  </si>
+  <si>
+    <t>420723.03</t>
+  </si>
+  <si>
+    <t>2025-02-21</t>
+  </si>
+  <si>
+    <t>422873.03</t>
+  </si>
+  <si>
+    <t>424773.03</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>425143.03</t>
+  </si>
+  <si>
+    <t>428958.03</t>
+  </si>
+  <si>
+    <t>430278.03</t>
+  </si>
+  <si>
+    <t>431778.03</t>
+  </si>
+  <si>
+    <t>2025-03-02</t>
+  </si>
+  <si>
+    <t>432928.03</t>
+  </si>
+  <si>
+    <t>433298.03</t>
+  </si>
+  <si>
+    <t>434978.03</t>
+  </si>
+  <si>
+    <t>436742.03</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>440865.03</t>
+  </si>
+  <si>
+    <t>2025-03-07</t>
+  </si>
+  <si>
+    <t>445015.12</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>451015.12</t>
+  </si>
+  <si>
+    <t>451965.12</t>
+  </si>
+  <si>
+    <t>457965.12</t>
+  </si>
+  <si>
+    <t>2025-03-10</t>
+  </si>
+  <si>
+    <t>461065.12</t>
+  </si>
+  <si>
+    <t>466665.12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>474615.12</t>
+  </si>
+  <si>
+    <t>476498.8</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>477758.8</t>
+  </si>
+  <si>
+    <t>484358.8</t>
+  </si>
+  <si>
+    <t>2025-03-19</t>
+  </si>
+  <si>
+    <t>488558.8</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>495158.8</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>498893.8</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>502043.8</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>505193.8</t>
+  </si>
+  <si>
+    <t>506893.8</t>
+  </si>
+  <si>
+    <t>2025-04-02</t>
+  </si>
+  <si>
+    <t>508793.8</t>
+  </si>
+  <si>
+    <t>513383.8</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>516134.28</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>517154.62</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>523529.62</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>524929.6</t>
+  </si>
+  <si>
+    <t>529849.6</t>
+  </si>
+  <si>
+    <t>2025-04-08</t>
+  </si>
+  <si>
+    <t>536569.6</t>
+  </si>
+  <si>
+    <t>540469.6</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>547469.6</t>
+  </si>
+  <si>
+    <t>547589.6</t>
+  </si>
+  <si>
+    <t>548889.6</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>553209.6</t>
+  </si>
+  <si>
+    <t>558159.6</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>560659.6</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>563159.6</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>564659.6</t>
+  </si>
+  <si>
+    <t>566159.6</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>569699.6</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>574739.6</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>581179.6</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>579209.6</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>577634.6</t>
+  </si>
+  <si>
+    <t>578189</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>578466.2</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>582466.2</t>
+  </si>
+  <si>
+    <t>584966.2</t>
+  </si>
+  <si>
+    <t>588466.2</t>
+  </si>
+  <si>
+    <t>m_l_enterprises</t>
+  </si>
+  <si>
+    <t>598366.2</t>
+  </si>
+  <si>
+    <t>592666.239</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>598666.239</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>604666.239</t>
+  </si>
+  <si>
+    <t>608866.239</t>
+  </si>
+  <si>
+    <t>611566.239</t>
+  </si>
+  <si>
+    <t>613816.239</t>
+  </si>
+  <si>
+    <t>616666.239</t>
+  </si>
+  <si>
+    <t>618786.239</t>
+  </si>
+  <si>
+    <t>620906.239</t>
+  </si>
+  <si>
+    <t>625306.239</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>630506.239</t>
+  </si>
+  <si>
+    <t>633906.239</t>
+  </si>
+  <si>
+    <t>635136.239</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>639556.239</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>640681.239</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>646441.239</t>
+  </si>
+  <si>
+    <t>650101.239</t>
+  </si>
+  <si>
+    <t>2025-06-02</t>
+  </si>
+  <si>
+    <t>650311.239</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>651177.489</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>651754.989</t>
+  </si>
+  <si>
+    <t>646014.989</t>
+  </si>
+  <si>
+    <t>2025-06-04</t>
+  </si>
+  <si>
+    <t>649854.989</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>652854.989</t>
+  </si>
+  <si>
+    <t>653394.989</t>
+  </si>
+  <si>
+    <t>654276.989</t>
+  </si>
+  <si>
+    <t>2025-06-05</t>
+  </si>
+  <si>
+    <t>658276.989</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>658753.4265</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>660953.4265</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>662853.4265</t>
+  </si>
+  <si>
+    <t>663908.6765</t>
+  </si>
+  <si>
+    <t>666008.6765</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>667433.6765</t>
+  </si>
+  <si>
+    <t>669073.6765</t>
+  </si>
+  <si>
+    <t>669146.1265</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>669272.1265</t>
+  </si>
+  <si>
+    <t>669356.1265</t>
+  </si>
+  <si>
+    <t>671156.1265</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>673856.1265</t>
+  </si>
+  <si>
+    <t>675256.1265</t>
+  </si>
+  <si>
+    <t>683806.1265</t>
+  </si>
+  <si>
+    <t>2025-07-03</t>
+  </si>
+  <si>
+    <t>687166.1265</t>
+  </si>
+  <si>
+    <t>689916.1265</t>
+  </si>
+  <si>
+    <t>691316.1265</t>
+  </si>
+  <si>
+    <t>692387.1265</t>
+  </si>
+  <si>
+    <t>2025-07-06</t>
+  </si>
+  <si>
+    <t>692807.1265</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>693707.1265</t>
+  </si>
+  <si>
+    <t>694607.1265</t>
+  </si>
+  <si>
+    <t>695857.1265</t>
+  </si>
+  <si>
+    <t>696407.1265</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>696907.1265</t>
+  </si>
+  <si>
+    <t>692137.1265</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>689917.111458</t>
+  </si>
+  <si>
+    <t>690667.511458</t>
+  </si>
+  <si>
+    <t>690768.311458</t>
+  </si>
+  <si>
+    <t>693768.311458</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>696868.311458</t>
+  </si>
+  <si>
+    <t>699018.311458</t>
+  </si>
+  <si>
+    <t>701298.311458</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>705218.311458</t>
+  </si>
+  <si>
+    <t>705354.811458</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>711554.811458</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>713654.811458</t>
+  </si>
+  <si>
+    <t>715474.811458</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>716646.611458</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>722946.611458</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>727626.611458</t>
+  </si>
+  <si>
+    <t>740226.611458</t>
+  </si>
+  <si>
+    <t>748226.611458</t>
+  </si>
+  <si>
+    <t>752826.611458</t>
+  </si>
+  <si>
+    <t>763326.611458</t>
+  </si>
+  <si>
+    <t>768270.981458</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>769620.981458</t>
+  </si>
+  <si>
+    <t>771120.981458</t>
+  </si>
+  <si>
+    <t>772670.981458</t>
+  </si>
+  <si>
+    <t>774470.981458</t>
+  </si>
+  <si>
+    <t>776670.981458</t>
+  </si>
+  <si>
+    <t>777111.981458</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>784011.981458</t>
+  </si>
+  <si>
+    <t>790011.981458</t>
+  </si>
+  <si>
+    <t>796131.981458</t>
+  </si>
+  <si>
+    <t>805583.981458</t>
+  </si>
+  <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>808833.981458</t>
+  </si>
+  <si>
+    <t>809593.981458</t>
+  </si>
+  <si>
+    <t>806806.981458</t>
+  </si>
+  <si>
+    <t>808636.981458</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>804766.981458</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>1636366.981458</t>
+  </si>
+  <si>
+    <t>1637198.581458</t>
+  </si>
+  <si>
+    <t>1638748.581458</t>
+  </si>
+  <si>
+    <t>2025-08-31</t>
+  </si>
+  <si>
+    <t>1640498.581458</t>
+  </si>
+  <si>
+    <t>1642498.581458</t>
+  </si>
+  <si>
+    <t>1643786.581458</t>
+  </si>
+  <si>
+    <t>1645074.581458</t>
+  </si>
+  <si>
+    <t>817496.581458</t>
+  </si>
+  <si>
+    <t>2025-09-07</t>
+  </si>
+  <si>
+    <t>818289.541458</t>
+  </si>
+  <si>
+    <t>822452.581458</t>
+  </si>
+  <si>
+    <t>822662.149458</t>
+  </si>
+  <si>
+    <t>822916.949458</t>
+  </si>
+  <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>823902.549458</t>
+  </si>
+  <si>
+    <t>830891.349458</t>
+  </si>
+  <si>
+    <t>837161.109458</t>
+  </si>
+  <si>
+    <t>2025-09-15</t>
+  </si>
+  <si>
+    <t>839378.709458</t>
+  </si>
+  <si>
+    <t>848478.709458</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>851178.709458</t>
+  </si>
+  <si>
+    <t>857213.709458</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>861398.709458</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>862212.459458</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>863866.209458</t>
+  </si>
+  <si>
+    <t>863726.208758</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>863656.208408</t>
+  </si>
+  <si>
+    <t>863586.208058</t>
+  </si>
+  <si>
+    <t>863516.207708</t>
+  </si>
+  <si>
+    <t>863281.207208</t>
+  </si>
+  <si>
+    <t>863106.634208</t>
+  </si>
+  <si>
+    <t>del p</t>
+  </si>
+  <si>
+    <t>863421.204908</t>
+  </si>
+  <si>
+    <t>863656.205408</t>
+  </si>
+  <si>
+    <t>863726.205758</t>
+  </si>
+  <si>
+    <t>863796.206108</t>
+  </si>
+  <si>
+    <t>863866.206458</t>
+  </si>
+  <si>
+    <t>863036.630708</t>
+  </si>
+  <si>
+    <t>863001.628958</t>
+  </si>
+  <si>
+    <t>863796.202958</t>
+  </si>
+  <si>
+    <t>862968.294608</t>
+  </si>
+  <si>
+    <t>862901.625908</t>
+  </si>
+  <si>
+    <t>863799.537758</t>
+  </si>
+  <si>
+    <t>862768.632908</t>
+  </si>
+  <si>
+    <t>862702.136408</t>
+  </si>
+  <si>
+    <t>862635.636338</t>
+  </si>
+  <si>
+    <t>862569.136268</t>
+  </si>
+  <si>
+    <t>862345.325618</t>
+  </si>
+  <si>
+    <t>862179.065468</t>
+  </si>
+  <si>
+    <t>863309.906168</t>
+  </si>
+  <si>
+    <t>862012.808468</t>
+  </si>
+  <si>
+    <t>864624.149168</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>865548.149168</t>
+  </si>
+  <si>
+    <t>867973.649168</t>
+  </si>
+  <si>
+    <t>871977.299168</t>
+  </si>
+  <si>
+    <t>873627.299168</t>
+  </si>
+  <si>
+    <t>2025-10-04</t>
+  </si>
+  <si>
+    <t>877587.299168</t>
+  </si>
+  <si>
+    <t>882387.299168</t>
+  </si>
+  <si>
+    <t>2025-10-08</t>
+  </si>
+  <si>
+    <t>886467.299168</t>
+  </si>
+  <si>
+    <t>886967.299168</t>
+  </si>
+  <si>
+    <t>895367.299168</t>
+  </si>
+  <si>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>895897.549168</t>
+  </si>
+  <si>
+    <t>2025-10-09</t>
+  </si>
+  <si>
+    <t>896475.049168</t>
+  </si>
+  <si>
+    <t>898225.049168</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>902625.049168</t>
+  </si>
+  <si>
+    <t>905825.049168</t>
+  </si>
+  <si>
+    <t>911325.049168</t>
+  </si>
+  <si>
+    <t>915485.049168</t>
+  </si>
+  <si>
+    <t>918235.049168</t>
+  </si>
+  <si>
+    <t>2025-10-19</t>
+  </si>
+  <si>
+    <t>924835.049168</t>
+  </si>
+  <si>
+    <t>927385.049168</t>
+  </si>
+  <si>
+    <t>928985.049168</t>
+  </si>
+  <si>
+    <t>933215.049168</t>
+  </si>
+  <si>
+    <t>933138.859173</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>932915.049573</t>
+  </si>
+  <si>
+    <t>929045.049573</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>927819.048573</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>924819.028263</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>924583.819863</t>
+  </si>
+  <si>
+    <t>924358.216863</t>
+  </si>
+  <si>
+    <t>931318.216863</t>
+  </si>
+  <si>
+    <t>937643.216863</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>939228.716863</t>
+  </si>
+  <si>
+    <t>946486.316863</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>949745.516863</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>962918.816863</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>968078.516863</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>970670.516863</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>973958.516863</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>980958.516863</t>
+  </si>
+  <si>
+    <t>992358.516863</t>
+  </si>
+  <si>
+    <t>995208.516863</t>
+  </si>
+  <si>
+    <t>998070.516863</t>
+  </si>
+  <si>
+    <t>1005998.016863</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>1009893.516863</t>
+  </si>
+  <si>
+    <t>1015141.416863</t>
+  </si>
+  <si>
+    <t>1033141.416863</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>1039741.416863</t>
+  </si>
+  <si>
+    <t>1043041.416863</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>1045441.416863</t>
+  </si>
+  <si>
+    <t>1049441.416863</t>
+  </si>
+  <si>
+    <t>1052041.416863</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>1055641.416863</t>
+  </si>
+  <si>
+    <t>1058941.416863</t>
+  </si>
+  <si>
+    <t>1062241.416863</t>
+  </si>
+  <si>
+    <t>1062751.416863</t>
+  </si>
+  <si>
+    <t>1058881.416863</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>1066162.866863</t>
+  </si>
+  <si>
+    <t>1068493.866863</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>1076599.866863</t>
+  </si>
+  <si>
+    <t>1081765.866863</t>
+  </si>
+  <si>
+    <t>1083078.366863</t>
+  </si>
+  <si>
+    <t>1076628.366863</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>bhotika_marketing_group</t>
+  </si>
+  <si>
+    <t>1074228.066863</t>
+  </si>
+  <si>
+    <t>1078428.066863</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>1082628.066863</t>
+  </si>
+  <si>
+    <t>1087828.066863</t>
+  </si>
+  <si>
+    <t>1093108.066863</t>
+  </si>
+  <si>
+    <t>1088208.066863</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>1083408.066863</t>
+  </si>
+  <si>
+    <t>1080408.066863</t>
+  </si>
+  <si>
+    <t>1092223.559363</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>1104031.334363</t>
+  </si>
+  <si>
+    <t>1118031.334363</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>1127271.334363</t>
+  </si>
+  <si>
+    <t>1132071.334363</t>
+  </si>
+  <si>
+    <t>1135311.334363</t>
+  </si>
+  <si>
+    <t>1121795.852363</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>1121261.858063</t>
+  </si>
+  <si>
+    <t>1131021.858063</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>1137495.108063</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>1142220.108063</t>
+  </si>
+  <si>
+    <t>1146220.608063</t>
+  </si>
+  <si>
+    <t>1150745.320563</t>
+  </si>
+  <si>
+    <t>1157345.320563</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>1164145.320563</t>
+  </si>
+  <si>
+    <t>1170945.320563</t>
+  </si>
+  <si>
+    <t>1177545.320563</t>
+  </si>
+  <si>
+    <t>1178733.320563</t>
+  </si>
+  <si>
+    <t>1164513.270563</t>
+  </si>
+  <si>
+    <t>1162613.190563</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>1160613.203063</t>
+  </si>
+  <si>
+    <t>1158613.189313</t>
+  </si>
+  <si>
+    <t>1166276.091813</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>1171946.406813</t>
+  </si>
+  <si>
+    <t>1170783.496813</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>1175733.496813</t>
+  </si>
+  <si>
+    <t>1177833.496813</t>
+  </si>
+  <si>
+    <t>1180633.496813</t>
+  </si>
+  <si>
+    <t>1181833.496813</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>1188963.496813</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>1196783.496813</t>
+  </si>
+  <si>
+    <t>1204868.496813</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>1212900.996813</t>
+  </si>
+  <si>
+    <t>1220074.996813</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>1223077.996813</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>1224715.996813</t>
+  </si>
+  <si>
+    <t>1226899.996813</t>
+  </si>
+  <si>
+    <t>1229083.996813</t>
+  </si>
+  <si>
+    <t>1231183.996813</t>
+  </si>
+  <si>
+    <t>1235515.246813</t>
+  </si>
+  <si>
+    <t>1236071.746813</t>
+  </si>
+  <si>
+    <t>1245655.746813</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>1250065.746813</t>
+  </si>
+  <si>
+    <t>1250865.746813</t>
+  </si>
+  <si>
+    <t>yash_agencies</t>
+  </si>
+  <si>
+    <t>1233981.742613</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>1231381.742613</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>1230791.747613</t>
+  </si>
+  <si>
+    <t>1230601.739613</t>
+  </si>
+  <si>
+    <t>1232124.239613</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>1234674.239613</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>1237866.239613</t>
+  </si>
+  <si>
+    <t>1241226.239613</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>1242150.239613</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>1244701.739613</t>
+  </si>
+  <si>
+    <t>1245339.089613</t>
+  </si>
+  <si>
+    <t>1248939.089613</t>
+  </si>
+  <si>
+    <t>1253139.089613</t>
+  </si>
+  <si>
+    <t>1254259.089613</t>
+  </si>
+  <si>
+    <t>1261139.089613</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>1277139.089613</t>
+  </si>
+  <si>
+    <t>1296567.089613</t>
+  </si>
+  <si>
+    <t>1263422.839613</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>1266662.839613</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>1264082.839613</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>1263482.839613</t>
+  </si>
+  <si>
+    <t>1262462.838113</t>
+  </si>
+  <si>
+    <t>1213261.350113</t>
+  </si>
+  <si>
+    <t>1164060.870113</t>
+  </si>
+  <si>
+    <t>1213262.358113</t>
+  </si>
+  <si>
+    <t>1210062.378113</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>1209242.328113</t>
+  </si>
+  <si>
+    <t>1207242.288113</t>
+  </si>
+  <si>
+    <t>1227979.788113</t>
+  </si>
+  <si>
+    <t>1235179.788113</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>1239379.788113</t>
+  </si>
+  <si>
+    <t>1242979.788113</t>
+  </si>
+  <si>
+    <t>1246879.788113</t>
+  </si>
+  <si>
+    <t>1249503.788113</t>
+  </si>
+  <si>
+    <t>SuryaDhara_Dhaba</t>
+  </si>
+  <si>
+    <t>1253403.788113</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
+  </si>
+  <si>
+    <t>1256103.788113</t>
+  </si>
+  <si>
+    <t>1259103.788113</t>
+  </si>
+  <si>
+    <t>1263153.788113</t>
+  </si>
+  <si>
+    <t>1267317.788113</t>
+  </si>
+  <si>
+    <t>1267737.788113</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
+  </si>
+  <si>
+    <t>1271885.288113</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>1275161.288113</t>
+  </si>
+  <si>
+    <t>1280234.048113</t>
+  </si>
+  <si>
+    <t>1282274.048113</t>
+  </si>
+  <si>
+    <t>1287034.048113</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>1296378.048113</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>1298037.048113</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>1295637.063113</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>1291767.063113</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>1290917.067113</t>
+  </si>
+  <si>
+    <t>1296017.067113</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>1298057.067113</t>
+  </si>
+  <si>
+    <t>1303817.067113</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>1307267.067113</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>1310776.067113</t>
+  </si>
+  <si>
+    <t>1312036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>1319036.067113</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>1326836.067113</t>
+  </si>
+  <si>
+    <t>1327033.467113</t>
+  </si>
+  <si>
+    <t>1329797.067113</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>1329197.067113</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1335316.467113</t>
+  </si>
+  <si>
+    <t>1344316.467113</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1353916.467113</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>1359441.467113</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1359371.463613</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>1359304.263613</t>
+  </si>
+  <si>
+    <t>1359171.796813</t>
+  </si>
+  <si>
+    <t>1357641.778813</t>
+  </si>
+  <si>
+    <t>1355241.793813</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>1354041.801313</t>
+  </si>
+  <si>
+    <t>1353631.776313</t>
+  </si>
+  <si>
+    <t>1351276.776313</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>1348876.776313</t>
+  </si>
+  <si>
+    <t>1346926.776313</t>
+  </si>
+  <si>
+    <t>1347147.276313</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1352587.276313</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1354862.276313</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>1358062.276313</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>1359912.276313</t>
+  </si>
+  <si>
+    <t>1361466.276313</t>
+  </si>
+  <si>
+    <t>1365414.276313</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>1366816.026313</t>
+  </si>
+  <si>
+    <t>1367950.026313</t>
+  </si>
+  <si>
+    <t>1368735.426313</t>
+  </si>
+  <si>
+    <t>1362715.426313</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1362115.426313</t>
+  </si>
+  <si>
+    <t>1365515.426313</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>1369115.426313</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1374515.426313</t>
+  </si>
+  <si>
+    <t>1378295.426313</t>
+  </si>
+  <si>
+    <t>1379479.826313</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1380582.326313</t>
+  </si>
+  <si>
+    <t>1381648.076313</t>
+  </si>
+  <si>
+    <t>1385128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>1390528.076313</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>1394128.076313</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>1396228.076313</t>
+  </si>
+  <si>
+    <t>1398928.076313</t>
+  </si>
+  <si>
+    <t>1402528.076313</t>
+  </si>
+  <si>
+    <t>1404448.076313</t>
+  </si>
+  <si>
+    <t>1403368.076313</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>1405168.076313</t>
+  </si>
+  <si>
+    <t>1406968.076313</t>
+  </si>
+  <si>
+    <t>1404818.069313</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>1403968.073313</t>
+  </si>
+  <si>
+    <t>1402438.055313</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>1401418.053813</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>1404178.053813</t>
+  </si>
+  <si>
+    <t>1407778.053813</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>1410538.053813</t>
+  </si>
+  <si>
+    <t>1408588.053813</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1410388.053813</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>1414236.053813</t>
+  </si>
+  <si>
+    <t>1416136.053813</t>
+  </si>
+  <si>
+    <t>1418836.053813</t>
+  </si>
+  <si>
+    <t>1421586.053813</t>
+  </si>
+  <si>
+    <t>1422586.053813</t>
+  </si>
+  <si>
+    <t>1422734.053813</t>
+  </si>
+  <si>
+    <t>1424634.053813</t>
+  </si>
+  <si>
+    <t>1427334.053813</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1430084.053813</t>
+  </si>
+  <si>
+    <t>1431084.053813</t>
+  </si>
+  <si>
+    <t>1441290.053813</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>1444916.753813</t>
+  </si>
+  <si>
+    <t>1440776.753813</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1440152.753813</t>
+  </si>
+  <si>
+    <t>1437372.753813</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>1436192.753813</t>
+  </si>
+  <si>
+    <t>1439792.753813</t>
+  </si>
+  <si>
+    <t>1441992.753813</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>1443592.753813</t>
+  </si>
+  <si>
+    <t>1446682.753813</t>
+  </si>
+  <si>
+    <t>1450182.753813</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1453982.753813</t>
+  </si>
+  <si>
+    <t>1457482.753813</t>
+  </si>
+  <si>
+    <t>1456462.752313</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>1458012.752313</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1459962.752313</t>
+  </si>
+  <si>
+    <t>1461512.752313</t>
+  </si>
+  <si>
+    <t>1465112.752313</t>
+  </si>
+  <si>
+    <t>1466302.752313</t>
+  </si>
+  <si>
+    <t>1468902.752313</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1472802.752313</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>1477002.752313</t>
+  </si>
+  <si>
+    <t>1480602.752313</t>
+  </si>
+  <si>
+    <t>1483902.752313</t>
+  </si>
+  <si>
+    <t>1485722.752313</t>
+  </si>
+  <si>
+    <t>1485512.332313</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>1483752.322313</t>
+  </si>
+  <si>
+    <t>1486952.322313</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>1491152.322313</t>
+  </si>
+  <si>
+    <t>1495252.322313</t>
+  </si>
+  <si>
+    <t>1495945.322313</t>
+  </si>
+  <si>
+    <t>1500145.322313</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>1503145.322313</t>
+  </si>
+  <si>
+    <t>1504945.322313</t>
+  </si>
+  <si>
+    <t>1508845.322313</t>
+  </si>
+  <si>
+    <t>1512345.322313</t>
+  </si>
+  <si>
+    <t>1517145.922313</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>1514385.922313</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>1513761.922313</t>
+  </si>
+  <si>
+    <t>1528041.922313</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>1529751.922313</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>1533351.922313</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>1547351.922313</t>
+  </si>
+  <si>
+    <t>1550276.922313</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>1551896.922313</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>1555196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>1557596.922313</t>
+  </si>
+  <si>
+    <t>1563196.922313</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>1569596.922313</t>
+  </si>
+  <si>
+    <t>1573596.922313</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>1577196.922313</t>
+  </si>
+  <si>
+    <t>1571716.922313</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>1571386.928313</t>
+  </si>
+  <si>
+    <t>1571056.934313</t>
+  </si>
+  <si>
+    <t>1570726.908813</t>
+  </si>
+  <si>
+    <t>1571716.898813</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>1570256.894813</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>1568855.294963</t>
+  </si>
+  <si>
+    <t>1568788.084988</t>
+  </si>
+  <si>
+    <t>1568720.875013</t>
+  </si>
+  <si>
+    <t>1568653.665038</t>
+  </si>
+  <si>
+    <t>1581510.369038</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>1589310.369038</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>1592610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>1594610.369038</t>
+  </si>
+  <si>
+    <t>1595610.369038</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>1593458.369038</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>1593247.949038</t>
+  </si>
+  <si>
+    <t>1592917.955038</t>
+  </si>
+  <si>
+    <t>1591897.953538</t>
+  </si>
+  <si>
+    <t>1597977.953538</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>1603227.953538</t>
+  </si>
+  <si>
+    <t>1609227.953538</t>
+  </si>
+  <si>
+    <t>1612827.953538</t>
+  </si>
+  <si>
+    <t>1616427.953538</t>
+  </si>
+  <si>
+    <t>1620027.953538</t>
+  </si>
+  <si>
+    <t>1620552.953538</t>
+  </si>
+  <si>
+    <t>1629343.553538</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>1629013.559538</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>1628413.558038</t>
+  </si>
+  <si>
+    <t>1630539.808038</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>1637574.808038</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
   </si>
   <si>
     <t>1647649.808038</t>
   </si>
   <si>
-    <t>utkarsh</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>pick_n_pay_store</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>46068</t>
-  </si>
-  <si>
-    <t>2020-04-19</t>
-  </si>
-  <si>
-    <t>55635</t>
-  </si>
-  <si>
-    <t>2020-05-03</t>
-  </si>
-  <si>
-    <t>42309</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>deena_nath_and_sons</t>
-  </si>
-  <si>
-    <t>pay</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>2020-04-20</t>
-  </si>
-  <si>
-    <t>29250</t>
-  </si>
-  <si>
-    <t>2020-05-02</t>
-  </si>
-  <si>
-    <t>gupta_dal_mills</t>
-  </si>
-  <si>
-    <t>42900</t>
-  </si>
-  <si>
-    <t>2020-05-23</t>
-  </si>
-  <si>
-    <t>21630</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>n_b_traders</t>
-  </si>
-  <si>
-    <t>10550</t>
-  </si>
-  <si>
-    <t>2020-05-09</t>
-  </si>
-  <si>
-    <t>naman_enterprises</t>
-  </si>
-  <si>
-    <t>15330</t>
-  </si>
-  <si>
-    <t>raj_shree_distributors</t>
-  </si>
-  <si>
-    <t>4118</t>
-  </si>
-  <si>
-    <t>ram_niwas_sarveshwar_kumar</t>
-  </si>
-  <si>
-    <t>16900</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>29646</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>24232</t>
-  </si>
-  <si>
-    <t>2020-05-30</t>
-  </si>
-  <si>
-    <t>21575</t>
-  </si>
-  <si>
-    <t>2020-06-06</t>
-  </si>
-  <si>
-    <t>parul_traders</t>
-  </si>
-  <si>
-    <t>18821</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>palm_tree_hotel_and_restaurent</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>43652</t>
-  </si>
-  <si>
-    <t>65785</t>
-  </si>
-  <si>
-    <t>2020-06-20</t>
-  </si>
-  <si>
-    <t>55984</t>
-  </si>
-  <si>
-    <t>21739</t>
-  </si>
-  <si>
-    <t>17620</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>ganga_traders</t>
-  </si>
-  <si>
-    <t>28917</t>
-  </si>
-  <si>
-    <t>2020-07-08</t>
-  </si>
-  <si>
-    <t>6420</t>
-  </si>
-  <si>
-    <t>40875</t>
-  </si>
-  <si>
-    <t>2020-07-06</t>
-  </si>
-  <si>
-    <t>56311</t>
-  </si>
-  <si>
-    <t>2020-06-26</t>
-  </si>
-  <si>
-    <t>25880</t>
-  </si>
-  <si>
-    <t>17750</t>
-  </si>
-  <si>
-    <t>42278</t>
-  </si>
-  <si>
-    <t>2020-07-10</t>
-  </si>
-  <si>
-    <t>sohan_lal_shri_kishan_das</t>
-  </si>
-  <si>
-    <t>22450</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>52465</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>krishna_enterprises</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>33390</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>34780</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>sagar_and_co</t>
-  </si>
-  <si>
-    <t>8664</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>vinod_kumar_pramod_kumar</t>
-  </si>
-  <si>
-    <t>19373</t>
-  </si>
-  <si>
-    <t>2020-08-11</t>
-  </si>
-  <si>
-    <t>cash</t>
-  </si>
-  <si>
-    <t>3820</t>
-  </si>
-  <si>
-    <t>2020-07-09</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>2020-10-01</t>
-  </si>
-  <si>
-    <t>33768</t>
-  </si>
-  <si>
-    <t>2020-09-20</t>
-  </si>
-  <si>
-    <t>48634</t>
-  </si>
-  <si>
-    <t>2020-08-06</t>
-  </si>
-  <si>
-    <t>78960</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>66511</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>82598</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>2020-10-13</t>
-  </si>
-  <si>
-    <t>29474</t>
-  </si>
-  <si>
-    <t>2020-08-08</t>
-  </si>
-  <si>
-    <t>43498</t>
-  </si>
-  <si>
-    <t>39550</t>
-  </si>
-  <si>
-    <t>2020-09-28</t>
-  </si>
-  <si>
-    <t>26333</t>
-  </si>
-  <si>
-    <t>2020-09-29</t>
-  </si>
-  <si>
-    <t>amar_distributors</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>26460</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>21945</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>10811</t>
-  </si>
-  <si>
-    <t>2020-10-15</t>
-  </si>
-  <si>
-    <t>22260</t>
-  </si>
-  <si>
-    <t>2020-10-17</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>2020-11-05</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>2020-10-26</t>
-  </si>
-  <si>
-    <t>2020-11-09</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>9548</t>
-  </si>
-  <si>
-    <t>2020-10-07</t>
-  </si>
-  <si>
-    <t>5414</t>
-  </si>
-  <si>
-    <t>85205</t>
-  </si>
-  <si>
-    <t>22948</t>
-  </si>
-  <si>
-    <t>2020-10-23</t>
-  </si>
-  <si>
-    <t>125752</t>
-  </si>
-  <si>
-    <t>105819</t>
-  </si>
-  <si>
-    <t>2020-11-08</t>
-  </si>
-  <si>
-    <t>28618</t>
-  </si>
-  <si>
-    <t>107210</t>
-  </si>
-  <si>
-    <t>2020-11-19</t>
-  </si>
-  <si>
-    <t>24600</t>
-  </si>
-  <si>
-    <t>royal_marketing_group</t>
-  </si>
-  <si>
-    <t>25700</t>
-  </si>
-  <si>
-    <t>2020-11-27</t>
-  </si>
-  <si>
-    <t>2020-12-05</t>
-  </si>
-  <si>
-    <t>26360</t>
-  </si>
-  <si>
-    <t>2020-12-07</t>
-  </si>
-  <si>
-    <t>242194</t>
-  </si>
-  <si>
-    <t>64450</t>
-  </si>
-  <si>
-    <t>46525</t>
-  </si>
-  <si>
-    <t>2020-12-06</t>
-  </si>
-  <si>
-    <t>46704</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>48657</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>26200</t>
-  </si>
-  <si>
-    <t>2020-12-27</t>
-  </si>
-  <si>
-    <t>34860</t>
-  </si>
-  <si>
-    <t>32810</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>haryana_palace_restaurent_and_bar_pvt_limited</t>
-  </si>
-  <si>
-    <t>6254</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>162431</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>250974</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>16533</t>
-  </si>
-  <si>
-    <t>2020-12-20</t>
-  </si>
-  <si>
-    <t>15771</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>radhey_dipartmental</t>
-  </si>
-  <si>
-    <t>15955</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>43550</t>
-  </si>
-  <si>
-    <t>maa_ganga_enterprises</t>
-  </si>
-  <si>
-    <t>26136</t>
-  </si>
-  <si>
-    <t>58500</t>
-  </si>
-  <si>
-    <t>64880</t>
-  </si>
-  <si>
-    <t>28560</t>
-  </si>
-  <si>
-    <t>49800</t>
-  </si>
-  <si>
-    <t>2021-03-22</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>2021-03-20</t>
-  </si>
-  <si>
-    <t>31215</t>
-  </si>
-  <si>
-    <t>194205</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>56050</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>202607</t>
-  </si>
-  <si>
-    <t>2021-02-16</t>
-  </si>
-  <si>
-    <t>110752</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>148920</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>31122</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>33750</t>
-  </si>
-  <si>
-    <t>2020-12-25</t>
-  </si>
-  <si>
-    <t>27600</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>102710</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>80350</t>
-  </si>
-  <si>
-    <t>2021-03-21</t>
-  </si>
-  <si>
-    <t>47250</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>10500</t>
-  </si>
-  <si>
-    <t>2021-04-06</t>
-  </si>
-  <si>
-    <t>44083.39</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>43250</t>
-  </si>
-  <si>
-    <t>34020</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>46050</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>30150</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>26880</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>2021-04-10</t>
-  </si>
-  <si>
-    <t>27201</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>2021-04-28</t>
-  </si>
-  <si>
-    <t>36536</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>28201</t>
-  </si>
-  <si>
-    <t>77606</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>23880</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>5434</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2021-01-03</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>2021-02-11</t>
-  </si>
-  <si>
-    <t>124571</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>51474</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>51119</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>26246</t>
-  </si>
-  <si>
-    <t>35767</t>
-  </si>
-  <si>
-    <t>17714</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>35266</t>
-  </si>
-  <si>
-    <t>39178</t>
-  </si>
-  <si>
-    <t>25316</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>8987</t>
-  </si>
-  <si>
-    <t>21147</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>20900</t>
-  </si>
-  <si>
-    <t>2021-05-11</t>
-  </si>
-  <si>
-    <t>59970</t>
-  </si>
-  <si>
-    <t>2021-01-31</t>
-  </si>
-  <si>
-    <t>54990</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>860</t>
-  </si>
-  <si>
-    <t>47870</t>
-  </si>
-  <si>
-    <t>5670</t>
-  </si>
-  <si>
-    <t>15335</t>
-  </si>
-  <si>
-    <t>91440</t>
-  </si>
-  <si>
-    <t>2021-06-04</t>
-  </si>
-  <si>
-    <t>17430</t>
-  </si>
-  <si>
-    <t>royal_marketing_company</t>
-  </si>
-  <si>
-    <t>35040</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>41300</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>29510</t>
-  </si>
-  <si>
-    <t>2021-06-14</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>2021-07-02</t>
-  </si>
-  <si>
-    <t>24350</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>3430</t>
-  </si>
-  <si>
-    <t>39740</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
-  </si>
-  <si>
-    <t>2021-08-17</t>
-  </si>
-  <si>
-    <t>38310</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>25200</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>2021-08-21</t>
-  </si>
-  <si>
-    <t>34200</t>
-  </si>
-  <si>
-    <t>33600</t>
-  </si>
-  <si>
-    <t>31200</t>
-  </si>
-  <si>
-    <t>34240</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>9264</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>32700</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>54540</t>
-  </si>
-  <si>
-    <t>41060</t>
-  </si>
-  <si>
-    <t>49156</t>
-  </si>
-  <si>
-    <t>48114</t>
-  </si>
-  <si>
-    <t>2021-09-21</t>
-  </si>
-  <si>
-    <t>chanchal_trading_company</t>
-  </si>
-  <si>
-    <t>18250</t>
-  </si>
-  <si>
-    <t>2021-08-08</t>
-  </si>
-  <si>
-    <t>97950</t>
-  </si>
-  <si>
-    <t>2021-08-10</t>
-  </si>
-  <si>
-    <t>52000</t>
-  </si>
-  <si>
-    <t>118530</t>
-  </si>
-  <si>
-    <t>9200</t>
-  </si>
-  <si>
-    <t>2021-06-19</t>
-  </si>
-  <si>
-    <t>74076</t>
-  </si>
-  <si>
-    <t>2021-05-29</t>
-  </si>
-  <si>
-    <t>33364</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>87172</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>40982</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>20905</t>
-  </si>
-  <si>
-    <t>121062</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>178358</t>
-  </si>
-  <si>
-    <t>117540</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>158935</t>
-  </si>
-  <si>
-    <t>96721</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>22244</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>25401</t>
-  </si>
-  <si>
-    <t>19234</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>24311</t>
-  </si>
-  <si>
-    <t>26391</t>
-  </si>
-  <si>
-    <t>15155</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>23339</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>16045</t>
-  </si>
-  <si>
-    <t>2021-05-22</t>
-  </si>
-  <si>
-    <t>20762</t>
-  </si>
-  <si>
-    <t>5692</t>
-  </si>
-  <si>
-    <t>9280</t>
-  </si>
-  <si>
-    <t>2021-06-29</t>
-  </si>
-  <si>
-    <t>11999</t>
-  </si>
-  <si>
-    <t>3665</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>8320</t>
-  </si>
-  <si>
-    <t>2021-07-17</t>
-  </si>
-  <si>
-    <t>10370</t>
-  </si>
-  <si>
-    <t>31531</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>13039</t>
-  </si>
-  <si>
-    <t>13717</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>14203</t>
-  </si>
-  <si>
-    <t>2021-09-18</t>
-  </si>
-  <si>
-    <t>9894</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>-79649</t>
-  </si>
-  <si>
-    <t>167596.95</t>
-  </si>
-  <si>
-    <t>-97079</t>
-  </si>
-  <si>
-    <t>sale</t>
-  </si>
-  <si>
-    <t>168576.95</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>169566.95</t>
-  </si>
-  <si>
-    <t>170526.95</t>
-  </si>
-  <si>
-    <t>172046.95</t>
-  </si>
-  <si>
-    <t>2021-08-14</t>
-  </si>
-  <si>
-    <t>174796.95</t>
-  </si>
-  <si>
-    <t>175046.95</t>
-  </si>
-  <si>
-    <t>177170.95</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
-  </si>
-  <si>
-    <t>-132119</t>
-  </si>
-  <si>
-    <t>-173419</t>
-  </si>
-  <si>
-    <t>-202929</t>
-  </si>
-  <si>
-    <t>-216929</t>
-  </si>
-  <si>
-    <t>-241279</t>
-  </si>
-  <si>
-    <t>-244709</t>
-  </si>
-  <si>
-    <t>-284449</t>
-  </si>
-  <si>
-    <t>-344449</t>
-  </si>
-  <si>
-    <t>-382759</t>
-  </si>
-  <si>
-    <t>-407959</t>
-  </si>
-  <si>
-    <t>-441959</t>
-  </si>
-  <si>
-    <t>-476159</t>
-  </si>
-  <si>
-    <t>-509759</t>
-  </si>
-  <si>
-    <t>-540959</t>
-  </si>
-  <si>
-    <t>-564959</t>
-  </si>
-  <si>
-    <t>-599199</t>
-  </si>
-  <si>
-    <t>167906.95</t>
-  </si>
-  <si>
-    <t>135206.95</t>
-  </si>
-  <si>
-    <t>-631749</t>
-  </si>
-  <si>
-    <t>-686289</t>
-  </si>
-  <si>
-    <t>-727349</t>
-  </si>
-  <si>
-    <t>-776505</t>
-  </si>
-  <si>
-    <t>-824619</t>
-  </si>
-  <si>
-    <t>116956.95</t>
-  </si>
-  <si>
-    <t>36956.95</t>
-  </si>
-  <si>
-    <t>-922569</t>
-  </si>
-  <si>
-    <t>-982569</t>
-  </si>
-  <si>
-    <t>-1034569</t>
-  </si>
-  <si>
-    <t>-1153099</t>
-  </si>
-  <si>
-    <t>-1143899</t>
-  </si>
-  <si>
-    <t>-1069823</t>
-  </si>
-  <si>
-    <t>-1036459</t>
-  </si>
-  <si>
-    <t>-949287</t>
-  </si>
-  <si>
-    <t>-908305</t>
-  </si>
-  <si>
-    <t>-808305</t>
-  </si>
-  <si>
-    <t>-787400</t>
-  </si>
-  <si>
-    <t>-666338</t>
-  </si>
-  <si>
-    <t>-487980</t>
-  </si>
-  <si>
-    <t>-370440</t>
-  </si>
-  <si>
-    <t>-211505</t>
-  </si>
-  <si>
-    <t>-114784</t>
-  </si>
-  <si>
-    <t>-92540</t>
-  </si>
-  <si>
-    <t>-67139</t>
-  </si>
-  <si>
-    <t>-47905</t>
-  </si>
-  <si>
-    <t>-23594</t>
-  </si>
-  <si>
-    <t>2797</t>
-  </si>
-  <si>
-    <t>17952</t>
-  </si>
-  <si>
-    <t>41291</t>
-  </si>
-  <si>
-    <t>71791</t>
-  </si>
-  <si>
-    <t>87836</t>
-  </si>
-  <si>
-    <t>108598</t>
-  </si>
-  <si>
-    <t>114290</t>
-  </si>
-  <si>
-    <t>123570</t>
-  </si>
-  <si>
-    <t>135569</t>
-  </si>
-  <si>
-    <t>139234</t>
-  </si>
-  <si>
-    <t>147554</t>
-  </si>
-  <si>
-    <t>157924</t>
-  </si>
-  <si>
-    <t>189455</t>
-  </si>
-  <si>
-    <t>196430</t>
-  </si>
-  <si>
-    <t>209469</t>
-  </si>
-  <si>
-    <t>223186</t>
-  </si>
-  <si>
-    <t>237389</t>
-  </si>
-  <si>
-    <t>247283</t>
-  </si>
-  <si>
-    <t>expns</t>
-  </si>
-  <si>
-    <t>246080</t>
-  </si>
-  <si>
-    <t>36956.96</t>
-  </si>
-  <si>
-    <t>238942</t>
-  </si>
-  <si>
-    <t>218942</t>
-  </si>
-  <si>
-    <t>218895</t>
-  </si>
-  <si>
-    <t>195775</t>
-  </si>
-  <si>
-    <t>176775</t>
-  </si>
-  <si>
-    <t>126775</t>
-  </si>
-  <si>
-    <t>125775</t>
-  </si>
-  <si>
-    <t>105775</t>
-  </si>
-  <si>
-    <t>104775</t>
-  </si>
-  <si>
-    <t>72275</t>
-  </si>
-  <si>
-    <t>pur</t>
-  </si>
-  <si>
-    <t>32231.96</t>
-  </si>
-  <si>
-    <t>2022-05-29</t>
-  </si>
-  <si>
-    <t>27931.96</t>
-  </si>
-  <si>
-    <t>28281.96</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>28951.96</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>30351.96</t>
-  </si>
-  <si>
-    <t>31791.96</t>
-  </si>
-  <si>
-    <t>33791.96</t>
-  </si>
-  <si>
-    <t>35991.96</t>
-  </si>
-  <si>
-    <t>38241.96</t>
-  </si>
-  <si>
-    <t>40481.96</t>
-  </si>
-  <si>
-    <t>44681.96</t>
-  </si>
-  <si>
-    <t>46571.96</t>
-  </si>
-  <si>
-    <t>2023-05-11</t>
-  </si>
-  <si>
-    <t>48524.96</t>
-  </si>
-  <si>
-    <t>49847.96</t>
-  </si>
-  <si>
-    <t>51149.96</t>
-  </si>
-  <si>
-    <t>52150.72</t>
-  </si>
-  <si>
-    <t>56000.72</t>
-  </si>
-  <si>
-    <t>2023-12-09</t>
-  </si>
-  <si>
-    <t>61209.72</t>
-  </si>
-  <si>
-    <t>65292.12</t>
-  </si>
-  <si>
-    <t>2024-01-14</t>
-  </si>
-  <si>
-    <t>70692.12</t>
-  </si>
-  <si>
-    <t>2024-01-13</t>
-  </si>
-  <si>
-    <t>72342.12</t>
-  </si>
-  <si>
-    <t>2024-01-18</t>
-  </si>
-  <si>
-    <t>74042.12</t>
-  </si>
-  <si>
-    <t>77042.12</t>
-  </si>
-  <si>
-    <t>78082.12</t>
-  </si>
-  <si>
-    <t>81127.12</t>
-  </si>
-  <si>
-    <t>2024-03-20</t>
-  </si>
-  <si>
-    <t>84172.12</t>
-  </si>
-  <si>
-    <t>87847.12</t>
-  </si>
-  <si>
-    <t>94421.52</t>
-  </si>
-  <si>
-    <t>2024-03-22</t>
-  </si>
-  <si>
-    <t>110421.52</t>
-  </si>
-  <si>
-    <t>2024-03-09</t>
-  </si>
-  <si>
-    <t>112821.52</t>
-  </si>
-  <si>
-    <t>116271.52</t>
-  </si>
-  <si>
-    <t>120171.52</t>
-  </si>
-  <si>
-    <t>132381.52</t>
-  </si>
-  <si>
-    <t>2024-03-12</t>
-  </si>
-  <si>
-    <t>133181.52</t>
-  </si>
-  <si>
-    <t>2024-03-13</t>
-  </si>
-  <si>
-    <t>134481.52</t>
-  </si>
-  <si>
-    <t>135941.52</t>
-  </si>
-  <si>
-    <t>134796.81</t>
-  </si>
-  <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
-    <t>135479.31</t>
-  </si>
-  <si>
-    <t>2024-05-15</t>
-  </si>
-  <si>
-    <t>136975.56</t>
-  </si>
-  <si>
-    <t>137684.31</t>
-  </si>
-  <si>
-    <t>138524.31</t>
-  </si>
-  <si>
-    <t>2024-05-20</t>
-  </si>
-  <si>
-    <t>139364.31</t>
-  </si>
-  <si>
-    <t>140724.31</t>
-  </si>
-  <si>
-    <t>141974.31</t>
-  </si>
-  <si>
-    <t>2024-05-22</t>
-  </si>
-  <si>
-    <t>144274.31</t>
-  </si>
-  <si>
-    <t>146974.31</t>
-  </si>
-  <si>
-    <t>2024-05-27</t>
-  </si>
-  <si>
-    <t>151354.31</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>151794.31</t>
-  </si>
-  <si>
-    <t>154754.31</t>
-  </si>
-  <si>
-    <t>156194.31</t>
-  </si>
-  <si>
-    <t>166851.81</t>
-  </si>
-  <si>
-    <t>167943.81</t>
-  </si>
-  <si>
-    <t>168321.81</t>
-  </si>
-  <si>
-    <t>169067.31</t>
-  </si>
-  <si>
-    <t>169959.81</t>
-  </si>
-  <si>
-    <t>170406.06</t>
-  </si>
-  <si>
-    <t>171078.06</t>
-  </si>
-  <si>
-    <t>173430.06</t>
-  </si>
-  <si>
-    <t>174585.06</t>
-  </si>
-  <si>
-    <t>177063.06</t>
-  </si>
-  <si>
-    <t>CITY_TRADERS</t>
-  </si>
-  <si>
-    <t>172570.56</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>174010.56</t>
-  </si>
-  <si>
-    <t>2024-07-03</t>
-  </si>
-  <si>
-    <t>175760.56</t>
-  </si>
-  <si>
-    <t>2024-07-12</t>
-  </si>
-  <si>
-    <t>176960.56</t>
-  </si>
-  <si>
-    <t>179260.56</t>
-  </si>
-  <si>
-    <t>182334.97</t>
-  </si>
-  <si>
-    <t>2024-07-01</t>
-  </si>
-  <si>
-    <t>185274.97</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>186975.97</t>
-  </si>
-  <si>
-    <t>189285.97</t>
-  </si>
-  <si>
-    <t>192285.97</t>
-  </si>
-  <si>
-    <t>195435.97</t>
-  </si>
-  <si>
-    <t>205935.97</t>
-  </si>
-  <si>
-    <t>206959.72</t>
-  </si>
-  <si>
-    <t>219349.72</t>
-  </si>
-  <si>
-    <t>221554.72</t>
-  </si>
-  <si>
-    <t>222279.22</t>
-  </si>
-  <si>
-    <t>222725.47</t>
-  </si>
-  <si>
-    <t>223066.72</t>
-  </si>
-  <si>
-    <t>225347.31</t>
-  </si>
-  <si>
-    <t>2024-07-13</t>
-  </si>
-  <si>
-    <t>223847.31</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>city_traders</t>
-  </si>
-  <si>
-    <t>220247.31</t>
-  </si>
-  <si>
-    <t>2024-07-11</t>
-  </si>
-  <si>
-    <t>221545.11</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>224594.31</t>
-  </si>
-  <si>
-    <t>225455.31</t>
-  </si>
-  <si>
-    <t>2024-07-24</t>
-  </si>
-  <si>
-    <t>225896.31</t>
-  </si>
-  <si>
-    <t>226796.31</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>227716.31</t>
-  </si>
-  <si>
-    <t>228966.31</t>
-  </si>
-  <si>
-    <t>2024-07-25</t>
-  </si>
-  <si>
-    <t>229286.31</t>
-  </si>
-  <si>
-    <t>235286.31</t>
-  </si>
-  <si>
-    <t>2024-07-30</t>
-  </si>
-  <si>
-    <t>238286.31</t>
-  </si>
-  <si>
-    <t>244686.31</t>
-  </si>
-  <si>
-    <t>251886.31</t>
-  </si>
-  <si>
-    <t>253136.31</t>
-  </si>
-  <si>
-    <t>257936.31</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>266336.3</t>
-  </si>
-  <si>
-    <t>268436.3</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>268676.3</t>
-  </si>
-  <si>
-    <t>2024-08-16</t>
-  </si>
-  <si>
-    <t>271526.3</t>
-  </si>
-  <si>
-    <t>284231.3</t>
-  </si>
-  <si>
-    <t>289691.3</t>
-  </si>
-  <si>
-    <t>293208.8</t>
-  </si>
-  <si>
-    <t>295098.8</t>
-  </si>
-  <si>
-    <t>296610.8</t>
-  </si>
-  <si>
-    <t>297925.7</t>
-  </si>
-  <si>
-    <t>2024-08-12</t>
-  </si>
-  <si>
-    <t>298597.7</t>
-  </si>
-  <si>
-    <t>2024-08-13</t>
-  </si>
-  <si>
-    <t>297881.66</t>
-  </si>
-  <si>
-    <t>2024-08-10</t>
-  </si>
-  <si>
-    <t>299681.7</t>
-  </si>
-  <si>
-    <t>2024-08-25</t>
-  </si>
-  <si>
-    <t>300681.7</t>
-  </si>
-  <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
-    <t>303481.7</t>
-  </si>
-  <si>
-    <t>309331.7</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>305731.7</t>
-  </si>
-  <si>
-    <t>2024-09-21</t>
-  </si>
-  <si>
-    <t>298006.72</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>304006.7</t>
-  </si>
-  <si>
-    <t>2024-09-18</t>
-  </si>
-  <si>
-    <t>306506.7</t>
-  </si>
-  <si>
-    <t>307706.7</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>309356.7</t>
-  </si>
-  <si>
-    <t>311996.7</t>
-  </si>
-  <si>
-    <t>313296.7</t>
-  </si>
-  <si>
-    <t>314146.7</t>
-  </si>
-  <si>
-    <t>dev_goldiee_agency</t>
-  </si>
-  <si>
-    <t>312346.66</t>
-  </si>
-  <si>
-    <t>2024-10-08</t>
-  </si>
-  <si>
-    <t>Bhotika_Marketing_Group</t>
-  </si>
-  <si>
-    <t>309597.06</t>
-  </si>
-  <si>
-    <t>2024-10-04</t>
-  </si>
-  <si>
-    <t>311697.06</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>311627.06</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>311557.06</t>
-  </si>
-  <si>
-    <t>311322.06</t>
-  </si>
-  <si>
-    <t>301084.56</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>290269.56</t>
-  </si>
-  <si>
-    <t>275149.56</t>
-  </si>
-  <si>
-    <t>271138.56</t>
-  </si>
-  <si>
-    <t>264334.56</t>
-  </si>
-  <si>
-    <t>264194.56</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>264072.06</t>
-  </si>
-  <si>
-    <t>263837.06</t>
-  </si>
-  <si>
-    <t>2024-11-10</t>
-  </si>
-  <si>
-    <t>263767.06</t>
-  </si>
-  <si>
-    <t>263697.06</t>
-  </si>
-  <si>
-    <t>263627.06</t>
-  </si>
-  <si>
-    <t>263557.06</t>
-  </si>
-  <si>
-    <t>262596.94</t>
-  </si>
-  <si>
-    <t>2024-11-08</t>
-  </si>
-  <si>
-    <t>264496.94</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>265896.94</t>
-  </si>
-  <si>
-    <t>268096.94</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>268346.94</t>
-  </si>
-  <si>
-    <t>271846.94</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>272476.94</t>
-  </si>
-  <si>
-    <t>2024-11-17</t>
-  </si>
-  <si>
-    <t>273106.94</t>
-  </si>
-  <si>
-    <t>273036.94</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>272966.94</t>
-  </si>
-  <si>
-    <t>272721.94</t>
-  </si>
-  <si>
-    <t>272529.94</t>
-  </si>
-  <si>
-    <t>276080.34</t>
-  </si>
-  <si>
-    <t>2024-12-05</t>
-  </si>
-  <si>
-    <t>277880.34</t>
-  </si>
-  <si>
-    <t>280880.34</t>
-  </si>
-  <si>
-    <t>282130.34</t>
-  </si>
-  <si>
-    <t>289630.34</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>294630.44</t>
-  </si>
-  <si>
-    <t>297780.44</t>
-  </si>
-  <si>
-    <t>2024-12-18</t>
-  </si>
-  <si>
-    <t>301230.44</t>
-  </si>
-  <si>
-    <t>306690.44</t>
-  </si>
-  <si>
-    <t>2024-12-21</t>
-  </si>
-  <si>
-    <t>308065.44</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>309797.94</t>
-  </si>
-  <si>
-    <t>2024-12-29</t>
-  </si>
-  <si>
-    <t>310327.12</t>
-  </si>
-  <si>
-    <t>315932.03</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>321270.03</t>
-  </si>
-  <si>
-    <t>316694.12</t>
-  </si>
-  <si>
-    <t>2025-01-13</t>
-  </si>
-  <si>
-    <t>318458.12</t>
-  </si>
-  <si>
-    <t>321765.62</t>
-  </si>
-  <si>
-    <t>323970.62</t>
-  </si>
-  <si>
-    <t>328370.62</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>330220.62</t>
-  </si>
-  <si>
-    <t>2025-01-15</t>
-  </si>
-  <si>
-    <t>332120.62</t>
-  </si>
-  <si>
-    <t>2025-01-20</t>
-  </si>
-  <si>
-    <t>334020.62</t>
-  </si>
-  <si>
-    <t>336420.62</t>
-  </si>
-  <si>
-    <t>340320.62</t>
-  </si>
-  <si>
-    <t>341520.62</t>
-  </si>
-  <si>
-    <t>343120.62</t>
-  </si>
-  <si>
-    <t>2025-01-23</t>
-  </si>
-  <si>
-    <t>343690.62</t>
-  </si>
-  <si>
-    <t>345040.62</t>
-  </si>
-  <si>
-    <t>2025-01-24</t>
-  </si>
-  <si>
-    <t>351040.62</t>
-  </si>
-  <si>
-    <t>353751.03</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>354647.03</t>
-  </si>
-  <si>
-    <t>361747.03</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>366397.03</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>367279.03</t>
-  </si>
-  <si>
-    <t>2025-02-01</t>
-  </si>
-  <si>
-    <t>368161.03</t>
-  </si>
-  <si>
-    <t>369368.53</t>
-  </si>
-  <si>
-    <t>368927.53</t>
-  </si>
-  <si>
-    <t>2025-02-16</t>
-  </si>
-  <si>
-    <t>369452.53</t>
-  </si>
-  <si>
-    <t>369715.03</t>
-  </si>
-  <si>
-    <t>370114.03</t>
-  </si>
-  <si>
-    <t>2025-02-26</t>
-  </si>
-  <si>
-    <t>370555.03</t>
-  </si>
-  <si>
-    <t>404323.03</t>
-  </si>
-  <si>
-    <t>2025-02-27</t>
-  </si>
-  <si>
-    <t>414223.03</t>
-  </si>
-  <si>
-    <t>2025-02-22</t>
-  </si>
-  <si>
-    <t>409873.03</t>
-  </si>
-  <si>
-    <t>2025-02-15</t>
-  </si>
-  <si>
-    <t>416023.03</t>
-  </si>
-  <si>
-    <t>418523.03</t>
-  </si>
-  <si>
-    <t>2025-02-19</t>
-  </si>
-  <si>
-    <t>419923.03</t>
-  </si>
-  <si>
-    <t>420723.03</t>
-  </si>
-  <si>
-    <t>2025-02-21</t>
-  </si>
-  <si>
-    <t>422873.03</t>
-  </si>
-  <si>
-    <t>424773.03</t>
-  </si>
-  <si>
-    <t>2025-02-23</t>
-  </si>
-  <si>
-    <t>425143.03</t>
-  </si>
-  <si>
-    <t>428958.03</t>
-  </si>
-  <si>
-    <t>430278.03</t>
-  </si>
-  <si>
-    <t>431778.03</t>
-  </si>
-  <si>
-    <t>2025-03-02</t>
-  </si>
-  <si>
-    <t>432928.03</t>
-  </si>
-  <si>
-    <t>433298.03</t>
-  </si>
-  <si>
-    <t>434978.03</t>
-  </si>
-  <si>
-    <t>436742.03</t>
-  </si>
-  <si>
-    <t>2025-02-28</t>
-  </si>
-  <si>
-    <t>440865.03</t>
-  </si>
-  <si>
-    <t>2025-03-07</t>
-  </si>
-  <si>
-    <t>445015.12</t>
-  </si>
-  <si>
-    <t>2025-03-08</t>
-  </si>
-  <si>
-    <t>451015.12</t>
-  </si>
-  <si>
-    <t>451965.12</t>
-  </si>
-  <si>
-    <t>457965.12</t>
-  </si>
-  <si>
-    <t>2025-03-10</t>
-  </si>
-  <si>
-    <t>461065.12</t>
-  </si>
-  <si>
-    <t>466665.12</t>
-  </si>
-  <si>
-    <t>2025-03-13</t>
-  </si>
-  <si>
-    <t>474615.12</t>
-  </si>
-  <si>
-    <t>476498.8</t>
-  </si>
-  <si>
-    <t>2025-03-03</t>
-  </si>
-  <si>
-    <t>477758.8</t>
-  </si>
-  <si>
-    <t>484358.8</t>
-  </si>
-  <si>
-    <t>2025-03-19</t>
-  </si>
-  <si>
-    <t>488558.8</t>
-  </si>
-  <si>
-    <t>2025-03-23</t>
-  </si>
-  <si>
-    <t>495158.8</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>498893.8</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>502043.8</t>
-  </si>
-  <si>
-    <t>2025-03-30</t>
-  </si>
-  <si>
-    <t>505193.8</t>
-  </si>
-  <si>
-    <t>506893.8</t>
-  </si>
-  <si>
-    <t>2025-04-02</t>
-  </si>
-  <si>
-    <t>508793.8</t>
-  </si>
-  <si>
-    <t>513383.8</t>
-  </si>
-  <si>
-    <t>2025-04-04</t>
-  </si>
-  <si>
-    <t>516134.28</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>517154.62</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>523529.62</t>
-  </si>
-  <si>
-    <t>2025-04-06</t>
-  </si>
-  <si>
-    <t>524929.6</t>
-  </si>
-  <si>
-    <t>529849.6</t>
-  </si>
-  <si>
-    <t>2025-04-08</t>
-  </si>
-  <si>
-    <t>536569.6</t>
-  </si>
-  <si>
-    <t>540469.6</t>
-  </si>
-  <si>
-    <t>2025-04-13</t>
-  </si>
-  <si>
-    <t>547469.6</t>
-  </si>
-  <si>
-    <t>547589.6</t>
-  </si>
-  <si>
-    <t>548889.6</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>553209.6</t>
-  </si>
-  <si>
-    <t>558159.6</t>
-  </si>
-  <si>
-    <t>2025-04-21</t>
-  </si>
-  <si>
-    <t>560659.6</t>
-  </si>
-  <si>
-    <t>2025-04-25</t>
-  </si>
-  <si>
-    <t>563159.6</t>
-  </si>
-  <si>
-    <t>2025-04-26</t>
-  </si>
-  <si>
-    <t>564659.6</t>
-  </si>
-  <si>
-    <t>566159.6</t>
-  </si>
-  <si>
-    <t>2025-04-27</t>
-  </si>
-  <si>
-    <t>569699.6</t>
-  </si>
-  <si>
-    <t>2025-04-29</t>
-  </si>
-  <si>
-    <t>574739.6</t>
-  </si>
-  <si>
-    <t>2025-05-01</t>
-  </si>
-  <si>
-    <t>581179.6</t>
-  </si>
-  <si>
-    <t>2025-05-05</t>
-  </si>
-  <si>
-    <t>579209.6</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>577634.6</t>
-  </si>
-  <si>
-    <t>578189</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>578466.2</t>
-  </si>
-  <si>
-    <t>2025-05-10</t>
-  </si>
-  <si>
-    <t>582466.2</t>
-  </si>
-  <si>
-    <t>584966.2</t>
-  </si>
-  <si>
-    <t>588466.2</t>
-  </si>
-  <si>
-    <t>m_l_enterprises</t>
-  </si>
-  <si>
-    <t>598366.2</t>
-  </si>
-  <si>
-    <t>592666.239</t>
-  </si>
-  <si>
-    <t>2025-05-14</t>
-  </si>
-  <si>
-    <t>598666.239</t>
-  </si>
-  <si>
-    <t>2025-05-19</t>
-  </si>
-  <si>
-    <t>604666.239</t>
-  </si>
-  <si>
-    <t>608866.239</t>
-  </si>
-  <si>
-    <t>611566.239</t>
-  </si>
-  <si>
-    <t>613816.239</t>
-  </si>
-  <si>
-    <t>616666.239</t>
-  </si>
-  <si>
-    <t>618786.239</t>
-  </si>
-  <si>
-    <t>620906.239</t>
-  </si>
-  <si>
-    <t>625306.239</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>630506.239</t>
-  </si>
-  <si>
-    <t>633906.239</t>
-  </si>
-  <si>
-    <t>635136.239</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>639556.239</t>
-  </si>
-  <si>
-    <t>2025-05-28</t>
-  </si>
-  <si>
-    <t>640681.239</t>
-  </si>
-  <si>
-    <t>2025-05-29</t>
-  </si>
-  <si>
-    <t>646441.239</t>
-  </si>
-  <si>
-    <t>650101.239</t>
-  </si>
-  <si>
-    <t>2025-06-02</t>
-  </si>
-  <si>
-    <t>650311.239</t>
-  </si>
-  <si>
-    <t>2025-05-15</t>
-  </si>
-  <si>
-    <t>651177.489</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>651754.989</t>
-  </si>
-  <si>
-    <t>646014.989</t>
-  </si>
-  <si>
-    <t>2025-06-04</t>
-  </si>
-  <si>
-    <t>649854.989</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>652854.989</t>
-  </si>
-  <si>
-    <t>653394.989</t>
-  </si>
-  <si>
-    <t>654276.989</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>658276.989</t>
-  </si>
-  <si>
-    <t>2025-06-12</t>
-  </si>
-  <si>
-    <t>658753.4265</t>
-  </si>
-  <si>
-    <t>2025-06-16</t>
-  </si>
-  <si>
-    <t>660953.4265</t>
-  </si>
-  <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>662853.4265</t>
-  </si>
-  <si>
-    <t>663908.6765</t>
-  </si>
-  <si>
-    <t>666008.6765</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>667433.6765</t>
-  </si>
-  <si>
-    <t>669073.6765</t>
-  </si>
-  <si>
-    <t>669146.1265</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>669272.1265</t>
-  </si>
-  <si>
-    <t>669356.1265</t>
-  </si>
-  <si>
-    <t>671156.1265</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>673856.1265</t>
-  </si>
-  <si>
-    <t>675256.1265</t>
-  </si>
-  <si>
-    <t>683806.1265</t>
-  </si>
-  <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>687166.1265</t>
-  </si>
-  <si>
-    <t>689916.1265</t>
-  </si>
-  <si>
-    <t>691316.1265</t>
-  </si>
-  <si>
-    <t>692387.1265</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>692807.1265</t>
-  </si>
-  <si>
-    <t>2025-07-09</t>
-  </si>
-  <si>
-    <t>693707.1265</t>
-  </si>
-  <si>
-    <t>694607.1265</t>
-  </si>
-  <si>
-    <t>695857.1265</t>
-  </si>
-  <si>
-    <t>696407.1265</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>696907.1265</t>
-  </si>
-  <si>
-    <t>692137.1265</t>
-  </si>
-  <si>
-    <t>2025-07-20</t>
-  </si>
-  <si>
-    <t>689917.111458</t>
-  </si>
-  <si>
-    <t>690667.511458</t>
-  </si>
-  <si>
-    <t>690768.311458</t>
-  </si>
-  <si>
-    <t>693768.311458</t>
-  </si>
-  <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>696868.311458</t>
-  </si>
-  <si>
-    <t>699018.311458</t>
-  </si>
-  <si>
-    <t>701298.311458</t>
-  </si>
-  <si>
-    <t>2025-07-19</t>
-  </si>
-  <si>
-    <t>705218.311458</t>
-  </si>
-  <si>
-    <t>705354.811458</t>
-  </si>
-  <si>
-    <t>2025-07-27</t>
-  </si>
-  <si>
-    <t>711554.811458</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>713654.811458</t>
-  </si>
-  <si>
-    <t>715474.811458</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>716646.611458</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>722946.611458</t>
-  </si>
-  <si>
-    <t>2025-08-08</t>
-  </si>
-  <si>
-    <t>727626.611458</t>
-  </si>
-  <si>
-    <t>740226.611458</t>
-  </si>
-  <si>
-    <t>748226.611458</t>
-  </si>
-  <si>
-    <t>752826.611458</t>
-  </si>
-  <si>
-    <t>763326.611458</t>
-  </si>
-  <si>
-    <t>768270.981458</t>
-  </si>
-  <si>
-    <t>2025-08-06</t>
-  </si>
-  <si>
-    <t>769620.981458</t>
-  </si>
-  <si>
-    <t>771120.981458</t>
-  </si>
-  <si>
-    <t>772670.981458</t>
-  </si>
-  <si>
-    <t>774470.981458</t>
-  </si>
-  <si>
-    <t>776670.981458</t>
-  </si>
-  <si>
-    <t>777111.981458</t>
-  </si>
-  <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>784011.981458</t>
-  </si>
-  <si>
-    <t>790011.981458</t>
-  </si>
-  <si>
-    <t>796131.981458</t>
-  </si>
-  <si>
-    <t>805583.981458</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
-    <t>808833.981458</t>
-  </si>
-  <si>
-    <t>809593.981458</t>
-  </si>
-  <si>
-    <t>806806.981458</t>
-  </si>
-  <si>
-    <t>808636.981458</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>804766.981458</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
-  </si>
-  <si>
-    <t>1636366.981458</t>
-  </si>
-  <si>
-    <t>1637198.581458</t>
-  </si>
-  <si>
-    <t>1638748.581458</t>
-  </si>
-  <si>
-    <t>2025-08-31</t>
-  </si>
-  <si>
-    <t>1640498.581458</t>
-  </si>
-  <si>
-    <t>1642498.581458</t>
-  </si>
-  <si>
-    <t>1643786.581458</t>
-  </si>
-  <si>
-    <t>1645074.581458</t>
-  </si>
-  <si>
-    <t>817496.581458</t>
-  </si>
-  <si>
-    <t>2025-09-07</t>
-  </si>
-  <si>
-    <t>818289.541458</t>
-  </si>
-  <si>
-    <t>822452.581458</t>
-  </si>
-  <si>
-    <t>822662.149458</t>
-  </si>
-  <si>
-    <t>822916.949458</t>
-  </si>
-  <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>823902.549458</t>
-  </si>
-  <si>
-    <t>830891.349458</t>
-  </si>
-  <si>
-    <t>837161.109458</t>
-  </si>
-  <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
-    <t>839378.709458</t>
-  </si>
-  <si>
-    <t>848478.709458</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>851178.709458</t>
-  </si>
-  <si>
-    <t>857213.709458</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>861398.709458</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>862212.459458</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>863866.209458</t>
-  </si>
-  <si>
-    <t>863726.208758</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>863656.208408</t>
-  </si>
-  <si>
-    <t>863586.208058</t>
-  </si>
-  <si>
-    <t>863516.207708</t>
-  </si>
-  <si>
-    <t>863281.207208</t>
-  </si>
-  <si>
-    <t>863106.634208</t>
-  </si>
-  <si>
-    <t>del p</t>
-  </si>
-  <si>
-    <t>863421.204908</t>
-  </si>
-  <si>
-    <t>863656.205408</t>
-  </si>
-  <si>
-    <t>863726.205758</t>
-  </si>
-  <si>
-    <t>863796.206108</t>
-  </si>
-  <si>
-    <t>863866.206458</t>
-  </si>
-  <si>
-    <t>863036.630708</t>
-  </si>
-  <si>
-    <t>863001.628958</t>
-  </si>
-  <si>
-    <t>863796.202958</t>
-  </si>
-  <si>
-    <t>862968.294608</t>
-  </si>
-  <si>
-    <t>862901.625908</t>
-  </si>
-  <si>
-    <t>863799.537758</t>
-  </si>
-  <si>
-    <t>862768.632908</t>
-  </si>
-  <si>
-    <t>862702.136408</t>
-  </si>
-  <si>
-    <t>862635.636338</t>
-  </si>
-  <si>
-    <t>862569.136268</t>
-  </si>
-  <si>
-    <t>862345.325618</t>
-  </si>
-  <si>
-    <t>862179.065468</t>
-  </si>
-  <si>
-    <t>863309.906168</t>
-  </si>
-  <si>
-    <t>862012.808468</t>
-  </si>
-  <si>
-    <t>864624.149168</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>865548.149168</t>
-  </si>
-  <si>
-    <t>867973.649168</t>
-  </si>
-  <si>
-    <t>871977.299168</t>
-  </si>
-  <si>
-    <t>873627.299168</t>
-  </si>
-  <si>
-    <t>2025-10-04</t>
-  </si>
-  <si>
-    <t>877587.299168</t>
-  </si>
-  <si>
-    <t>882387.299168</t>
-  </si>
-  <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
-    <t>886467.299168</t>
-  </si>
-  <si>
-    <t>886967.299168</t>
-  </si>
-  <si>
-    <t>895367.299168</t>
-  </si>
-  <si>
-    <t>2025-10-11</t>
-  </si>
-  <si>
-    <t>895897.549168</t>
-  </si>
-  <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>896475.049168</t>
-  </si>
-  <si>
-    <t>898225.049168</t>
-  </si>
-  <si>
-    <t>2025-10-17</t>
-  </si>
-  <si>
-    <t>902625.049168</t>
-  </si>
-  <si>
-    <t>905825.049168</t>
-  </si>
-  <si>
-    <t>911325.049168</t>
-  </si>
-  <si>
-    <t>915485.049168</t>
-  </si>
-  <si>
-    <t>918235.049168</t>
-  </si>
-  <si>
-    <t>2025-10-19</t>
-  </si>
-  <si>
-    <t>924835.049168</t>
-  </si>
-  <si>
-    <t>927385.049168</t>
-  </si>
-  <si>
-    <t>928985.049168</t>
-  </si>
-  <si>
-    <t>933215.049168</t>
-  </si>
-  <si>
-    <t>933138.859173</t>
-  </si>
-  <si>
-    <t>2025-11-05</t>
-  </si>
-  <si>
-    <t>932915.049573</t>
-  </si>
-  <si>
-    <t>929045.049573</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>927819.048573</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>924819.028263</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>924583.819863</t>
-  </si>
-  <si>
-    <t>924358.216863</t>
-  </si>
-  <si>
-    <t>931318.216863</t>
-  </si>
-  <si>
-    <t>937643.216863</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>939228.716863</t>
-  </si>
-  <si>
-    <t>946486.316863</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>949745.516863</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>962918.816863</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>968078.516863</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>970670.516863</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>973958.516863</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>980958.516863</t>
-  </si>
-  <si>
-    <t>992358.516863</t>
-  </si>
-  <si>
-    <t>995208.516863</t>
-  </si>
-  <si>
-    <t>998070.516863</t>
-  </si>
-  <si>
-    <t>1005998.016863</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>1009893.516863</t>
-  </si>
-  <si>
-    <t>1015141.416863</t>
-  </si>
-  <si>
-    <t>1033141.416863</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>1039741.416863</t>
-  </si>
-  <si>
-    <t>1043041.416863</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>1045441.416863</t>
-  </si>
-  <si>
-    <t>1049441.416863</t>
-  </si>
-  <si>
-    <t>1052041.416863</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>1055641.416863</t>
-  </si>
-  <si>
-    <t>1058941.416863</t>
-  </si>
-  <si>
-    <t>1062241.416863</t>
-  </si>
-  <si>
-    <t>1062751.416863</t>
-  </si>
-  <si>
-    <t>1058881.416863</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>1066162.866863</t>
-  </si>
-  <si>
-    <t>1068493.866863</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>1076599.866863</t>
-  </si>
-  <si>
-    <t>1081765.866863</t>
-  </si>
-  <si>
-    <t>1083078.366863</t>
-  </si>
-  <si>
-    <t>1076628.366863</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>bhotika_marketing_group</t>
-  </si>
-  <si>
-    <t>1074228.066863</t>
-  </si>
-  <si>
-    <t>1078428.066863</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>1082628.066863</t>
-  </si>
-  <si>
-    <t>1087828.066863</t>
-  </si>
-  <si>
-    <t>1093108.066863</t>
-  </si>
-  <si>
-    <t>1088208.066863</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>1083408.066863</t>
-  </si>
-  <si>
-    <t>1080408.066863</t>
-  </si>
-  <si>
-    <t>1092223.559363</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>1104031.334363</t>
-  </si>
-  <si>
-    <t>1118031.334363</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>1127271.334363</t>
-  </si>
-  <si>
-    <t>1132071.334363</t>
-  </si>
-  <si>
-    <t>1135311.334363</t>
-  </si>
-  <si>
-    <t>1121795.852363</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>1121261.858063</t>
-  </si>
-  <si>
-    <t>1131021.858063</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>1137495.108063</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>1142220.108063</t>
-  </si>
-  <si>
-    <t>1146220.608063</t>
-  </si>
-  <si>
-    <t>1150745.320563</t>
-  </si>
-  <si>
-    <t>1157345.320563</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>1164145.320563</t>
-  </si>
-  <si>
-    <t>1170945.320563</t>
-  </si>
-  <si>
-    <t>1177545.320563</t>
-  </si>
-  <si>
-    <t>1178733.320563</t>
-  </si>
-  <si>
-    <t>1164513.270563</t>
-  </si>
-  <si>
-    <t>1162613.190563</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>1160613.203063</t>
-  </si>
-  <si>
-    <t>1158613.189313</t>
-  </si>
-  <si>
-    <t>1166276.091813</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>1171946.406813</t>
-  </si>
-  <si>
-    <t>1170783.496813</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1175733.496813</t>
-  </si>
-  <si>
-    <t>1177833.496813</t>
-  </si>
-  <si>
-    <t>1180633.496813</t>
-  </si>
-  <si>
-    <t>1181833.496813</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>1188963.496813</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
-    <t>1196783.496813</t>
-  </si>
-  <si>
-    <t>1204868.496813</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
-  </si>
-  <si>
-    <t>1212900.996813</t>
-  </si>
-  <si>
-    <t>1220074.996813</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>1223077.996813</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>1224715.996813</t>
-  </si>
-  <si>
-    <t>1226899.996813</t>
-  </si>
-  <si>
-    <t>1229083.996813</t>
-  </si>
-  <si>
-    <t>1231183.996813</t>
-  </si>
-  <si>
-    <t>1235515.246813</t>
-  </si>
-  <si>
-    <t>1236071.746813</t>
-  </si>
-  <si>
-    <t>1245655.746813</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>1250065.746813</t>
-  </si>
-  <si>
-    <t>1250865.746813</t>
-  </si>
-  <si>
-    <t>yash_agencies</t>
-  </si>
-  <si>
-    <t>1233981.742613</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>1231381.742613</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>1230791.747613</t>
-  </si>
-  <si>
-    <t>1230601.739613</t>
-  </si>
-  <si>
-    <t>1232124.239613</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>1234674.239613</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>1237866.239613</t>
-  </si>
-  <si>
-    <t>1241226.239613</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>1242150.239613</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>1244701.739613</t>
-  </si>
-  <si>
-    <t>1245339.089613</t>
-  </si>
-  <si>
-    <t>1248939.089613</t>
-  </si>
-  <si>
-    <t>1253139.089613</t>
-  </si>
-  <si>
-    <t>1254259.089613</t>
-  </si>
-  <si>
-    <t>1261139.089613</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>1277139.089613</t>
-  </si>
-  <si>
-    <t>1296567.089613</t>
-  </si>
-  <si>
-    <t>1263422.839613</t>
-  </si>
-  <si>
-    <t>2026-04-18</t>
-  </si>
-  <si>
-    <t>1266662.839613</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
-    <t>1264082.839613</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>1263482.839613</t>
-  </si>
-  <si>
-    <t>1262462.838113</t>
-  </si>
-  <si>
-    <t>1213261.350113</t>
-  </si>
-  <si>
-    <t>1164060.870113</t>
-  </si>
-  <si>
-    <t>1213262.358113</t>
-  </si>
-  <si>
-    <t>1210062.378113</t>
-  </si>
-  <si>
-    <t>2026-04-11</t>
-  </si>
-  <si>
-    <t>1209242.328113</t>
-  </si>
-  <si>
-    <t>1207242.288113</t>
-  </si>
-  <si>
-    <t>1227979.788113</t>
-  </si>
-  <si>
-    <t>1235179.788113</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>1239379.788113</t>
-  </si>
-  <si>
-    <t>1242979.788113</t>
-  </si>
-  <si>
-    <t>1246879.788113</t>
-  </si>
-  <si>
-    <t>1249503.788113</t>
-  </si>
-  <si>
-    <t>SuryaDhara_Dhaba</t>
-  </si>
-  <si>
-    <t>1253403.788113</t>
-  </si>
-  <si>
-    <t>2026-04-25</t>
-  </si>
-  <si>
-    <t>1256103.788113</t>
-  </si>
-  <si>
-    <t>1259103.788113</t>
-  </si>
-  <si>
-    <t>1263153.788113</t>
-  </si>
-  <si>
-    <t>1267317.788113</t>
-  </si>
-  <si>
-    <t>1267737.788113</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>1271885.288113</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>1275161.288113</t>
-  </si>
-  <si>
-    <t>1280234.048113</t>
-  </si>
-  <si>
-    <t>1282274.048113</t>
-  </si>
-  <si>
-    <t>1287034.048113</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>1296378.048113</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>1298037.048113</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>1295637.063113</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>1291767.063113</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1290917.067113</t>
-  </si>
-  <si>
-    <t>1296017.067113</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>1298057.067113</t>
-  </si>
-  <si>
-    <t>1303817.067113</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>1307267.067113</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>1310776.067113</t>
-  </si>
-  <si>
-    <t>1312036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>1319036.067113</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>1326836.067113</t>
-  </si>
-  <si>
-    <t>1327033.467113</t>
-  </si>
-  <si>
-    <t>1329797.067113</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>1329197.067113</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>1335316.467113</t>
-  </si>
-  <si>
-    <t>1344316.467113</t>
-  </si>
-  <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
-    <t>1353916.467113</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>1359441.467113</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>1359371.463613</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>1359304.263613</t>
-  </si>
-  <si>
-    <t>1359171.796813</t>
-  </si>
-  <si>
-    <t>1357641.778813</t>
-  </si>
-  <si>
-    <t>1355241.793813</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>1354041.801313</t>
-  </si>
-  <si>
-    <t>1353631.776313</t>
-  </si>
-  <si>
-    <t>1351276.776313</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>1348876.776313</t>
-  </si>
-  <si>
-    <t>1346926.776313</t>
-  </si>
-  <si>
-    <t>1347147.276313</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>1352587.276313</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>1354862.276313</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>1358062.276313</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>1359912.276313</t>
-  </si>
-  <si>
-    <t>1361466.276313</t>
-  </si>
-  <si>
-    <t>1365414.276313</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>1366816.026313</t>
-  </si>
-  <si>
-    <t>1367950.026313</t>
-  </si>
-  <si>
-    <t>1368735.426313</t>
-  </si>
-  <si>
-    <t>1362715.426313</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>1362115.426313</t>
-  </si>
-  <si>
-    <t>1365515.426313</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>1369115.426313</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>1374515.426313</t>
-  </si>
-  <si>
-    <t>1378295.426313</t>
-  </si>
-  <si>
-    <t>1379479.826313</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>1380582.326313</t>
-  </si>
-  <si>
-    <t>1381648.076313</t>
-  </si>
-  <si>
-    <t>1385128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>1390528.076313</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>1394128.076313</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>1396228.076313</t>
-  </si>
-  <si>
-    <t>1398928.076313</t>
-  </si>
-  <si>
-    <t>1402528.076313</t>
-  </si>
-  <si>
-    <t>1404448.076313</t>
-  </si>
-  <si>
-    <t>1403368.076313</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>1405168.076313</t>
-  </si>
-  <si>
-    <t>1406968.076313</t>
-  </si>
-  <si>
-    <t>1404818.069313</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>1403968.073313</t>
-  </si>
-  <si>
-    <t>1402438.055313</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>1401418.053813</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>1404178.053813</t>
-  </si>
-  <si>
-    <t>1407778.053813</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>1410538.053813</t>
-  </si>
-  <si>
-    <t>1408588.053813</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>1410388.053813</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>1414236.053813</t>
-  </si>
-  <si>
-    <t>1416136.053813</t>
-  </si>
-  <si>
-    <t>1418836.053813</t>
-  </si>
-  <si>
-    <t>1421586.053813</t>
-  </si>
-  <si>
-    <t>1422586.053813</t>
-  </si>
-  <si>
-    <t>1422734.053813</t>
-  </si>
-  <si>
-    <t>1424634.053813</t>
-  </si>
-  <si>
-    <t>1427334.053813</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>1430084.053813</t>
-  </si>
-  <si>
-    <t>1431084.053813</t>
-  </si>
-  <si>
-    <t>1441290.053813</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>1444916.753813</t>
-  </si>
-  <si>
-    <t>1440776.753813</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>1440152.753813</t>
-  </si>
-  <si>
-    <t>1437372.753813</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>1436192.753813</t>
-  </si>
-  <si>
-    <t>1439792.753813</t>
-  </si>
-  <si>
-    <t>1441992.753813</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>1443592.753813</t>
-  </si>
-  <si>
-    <t>1446682.753813</t>
-  </si>
-  <si>
-    <t>1450182.753813</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>1453982.753813</t>
-  </si>
-  <si>
-    <t>1457482.753813</t>
-  </si>
-  <si>
-    <t>1456462.752313</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>1458012.752313</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>1459962.752313</t>
-  </si>
-  <si>
-    <t>1461512.752313</t>
-  </si>
-  <si>
-    <t>1465112.752313</t>
-  </si>
-  <si>
-    <t>1466302.752313</t>
-  </si>
-  <si>
-    <t>1468902.752313</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1472802.752313</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>1477002.752313</t>
-  </si>
-  <si>
-    <t>1480602.752313</t>
-  </si>
-  <si>
-    <t>1483902.752313</t>
-  </si>
-  <si>
-    <t>1485722.752313</t>
-  </si>
-  <si>
-    <t>1485512.332313</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>1483752.322313</t>
-  </si>
-  <si>
-    <t>1486952.322313</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>1491152.322313</t>
-  </si>
-  <si>
-    <t>1495252.322313</t>
-  </si>
-  <si>
-    <t>1495945.322313</t>
-  </si>
-  <si>
-    <t>1500145.322313</t>
-  </si>
-  <si>
-    <t>2026-08-30</t>
-  </si>
-  <si>
-    <t>1503145.322313</t>
-  </si>
-  <si>
-    <t>1504945.322313</t>
-  </si>
-  <si>
-    <t>1508845.322313</t>
-  </si>
-  <si>
-    <t>1512345.322313</t>
-  </si>
-  <si>
-    <t>1517145.922313</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>1514385.922313</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>1513761.922313</t>
-  </si>
-  <si>
-    <t>1528041.922313</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>1529751.922313</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>1533351.922313</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>1547351.922313</t>
-  </si>
-  <si>
-    <t>1550276.922313</t>
-  </si>
-  <si>
-    <t>2026-09-13</t>
-  </si>
-  <si>
-    <t>1551896.922313</t>
-  </si>
-  <si>
-    <t>2026-09-14</t>
-  </si>
-  <si>
-    <t>1555196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>1557596.922313</t>
-  </si>
-  <si>
-    <t>1563196.922313</t>
-  </si>
-  <si>
-    <t>2026-09-19</t>
-  </si>
-  <si>
-    <t>1569596.922313</t>
-  </si>
-  <si>
-    <t>1573596.922313</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>1577196.922313</t>
-  </si>
-  <si>
-    <t>1571716.922313</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>1571386.928313</t>
-  </si>
-  <si>
-    <t>1571056.934313</t>
-  </si>
-  <si>
-    <t>1570726.908813</t>
-  </si>
-  <si>
-    <t>1571716.898813</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>1570256.894813</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>1568855.294963</t>
-  </si>
-  <si>
-    <t>1568788.084988</t>
-  </si>
-  <si>
-    <t>1568720.875013</t>
-  </si>
-  <si>
-    <t>1568653.665038</t>
-  </si>
-  <si>
-    <t>1581510.369038</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>1589310.369038</t>
-  </si>
-  <si>
-    <t>2026-09-24</t>
-  </si>
-  <si>
-    <t>1592610.369038</t>
-  </si>
-  <si>
-    <t>2026-09-28</t>
-  </si>
-  <si>
-    <t>1594610.369038</t>
-  </si>
-  <si>
-    <t>1595610.369038</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
-    <t>1593458.369038</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
-  </si>
-  <si>
-    <t>1593247.949038</t>
-  </si>
-  <si>
-    <t>1592917.955038</t>
-  </si>
-  <si>
-    <t>1591897.953538</t>
-  </si>
-  <si>
-    <t>1597977.953538</t>
-  </si>
-  <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
-    <t>1603227.953538</t>
-  </si>
-  <si>
-    <t>1609227.953538</t>
-  </si>
-  <si>
-    <t>1612827.953538</t>
-  </si>
-  <si>
-    <t>1616427.953538</t>
-  </si>
-  <si>
-    <t>1620027.953538</t>
-  </si>
-  <si>
-    <t>1620552.953538</t>
-  </si>
-  <si>
-    <t>1629343.553538</t>
-  </si>
-  <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>1629013.559538</t>
-  </si>
-  <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
-    <t>1628413.558038</t>
-  </si>
-  <si>
-    <t>1630539.808038</t>
-  </si>
-  <si>
-    <t>2026-10-08</t>
-  </si>
-  <si>
-    <t>1637574.808038</t>
-  </si>
-  <si>
-    <t>2026-10-10</t>
-  </si>
-  <si>
     <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>1643649.780538</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>1640889.780538</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>1640289.780538</t>
+  </si>
+  <si>
+    <t>1655661.780538</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>1659835.530538</t>
+  </si>
+  <si>
+    <t>1663995.530538</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>1668155.530538</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>1670435.530538</t>
+  </si>
+  <si>
+    <t>2026-10-24</t>
   </si>
   <si>
     <t>arpit</t>
@@ -8234,7 +8279,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E797"/>
+  <dimension ref="A1:E805"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21780,10 +21825,146 @@
         <v>521</v>
       </c>
       <c r="D797" t="s">
-        <v>61</v>
+        <v>1525</v>
       </c>
       <c r="E797" t="s">
-        <v>1525</v>
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B798" t="s">
+        <v>522</v>
+      </c>
+      <c r="C798" t="s">
+        <v>521</v>
+      </c>
+      <c r="D798" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E798" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="s">
+        <v>630</v>
+      </c>
+      <c r="B799" t="s">
+        <v>522</v>
+      </c>
+      <c r="C799" t="s">
+        <v>521</v>
+      </c>
+      <c r="D799" t="s">
+        <v>1529</v>
+      </c>
+      <c r="E799" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="s">
+        <v>630</v>
+      </c>
+      <c r="B800" t="s">
+        <v>522</v>
+      </c>
+      <c r="C800" t="s">
+        <v>521</v>
+      </c>
+      <c r="D800" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E800" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="s">
+        <v>145</v>
+      </c>
+      <c r="B801" t="s">
+        <v>435</v>
+      </c>
+      <c r="C801" t="s">
+        <v>521</v>
+      </c>
+      <c r="D801" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E801" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="s">
+        <v>145</v>
+      </c>
+      <c r="B802" t="s">
+        <v>435</v>
+      </c>
+      <c r="C802" t="s">
+        <v>521</v>
+      </c>
+      <c r="D802" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E802" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B803" t="s">
+        <v>435</v>
+      </c>
+      <c r="C803" t="s">
+        <v>521</v>
+      </c>
+      <c r="D803" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E803" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="s">
+        <v>145</v>
+      </c>
+      <c r="B804" t="s">
+        <v>435</v>
+      </c>
+      <c r="C804" t="s">
+        <v>521</v>
+      </c>
+      <c r="D804" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E804" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="s">
+        <v>145</v>
+      </c>
+      <c r="B805" t="s">
+        <v>435</v>
+      </c>
+      <c r="C805" t="s">
+        <v>521</v>
+      </c>
+      <c r="D805" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E805" t="s">
+        <v>1540</v>
       </c>
     </row>
   </sheetData>
@@ -21798,13 +21979,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D1" t="s">
         <v>333</v>
@@ -21812,13 +21993,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D2" t="s">
         <v>333</v>
@@ -21826,13 +22007,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D3" t="s">
         <v>333</v>
@@ -21840,13 +22021,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -21854,13 +22035,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -21868,13 +22049,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D6" t="s">
         <v>333</v>
@@ -21882,13 +22063,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D7" t="s">
         <v>333</v>
@@ -21896,13 +22077,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="D8" t="s">
         <v>333</v>
@@ -21910,13 +22091,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1529</v>
+        <v>1544</v>
       </c>
       <c r="D9" t="s">
         <v>333</v>
@@ -21934,13 +22115,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>1530</v>
+        <v>1545</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -21951,13 +22132,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1531</v>
+        <v>1546</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -21968,13 +22149,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -21985,13 +22166,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>1533</v>
+        <v>1548</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -22002,13 +22183,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>1534</v>
+        <v>1549</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -22019,13 +22200,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B6" t="s">
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>1535</v>
+        <v>1550</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -22036,13 +22217,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>1536</v>
+        <v>1551</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
@@ -22053,13 +22234,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>1537</v>
+        <v>1552</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
@@ -22070,13 +22251,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>1538</v>
+        <v>1553</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
